--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="108">
   <si>
     <t>Viernes</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>JORGE ARTURO BERNAL MARIN</t>
+  </si>
+  <si>
+    <t>Ausencia</t>
   </si>
   <si>
     <t>15:30 - 21:00</t>
@@ -341,7 +344,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -382,6 +385,11 @@
     <font>
       <sz val="8.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -491,14 +499,6 @@
       </bottom>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -509,11 +509,19 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -577,10 +585,10 @@
     <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -601,13 +609,13 @@
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -616,11 +624,14 @@
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -628,7 +639,7 @@
     <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -637,13 +648,13 @@
     <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -862,7 +873,19 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="32" width="43.5"/>
+    <col customWidth="1" min="1" max="1" width="34.38"/>
+    <col customWidth="1" min="2" max="2" width="28.38"/>
+    <col customWidth="1" min="3" max="3" width="24.38"/>
+    <col customWidth="1" min="4" max="5" width="22.13"/>
+    <col customWidth="1" min="6" max="6" width="24.5"/>
+    <col customWidth="1" min="7" max="7" width="25.5"/>
+    <col customWidth="1" min="8" max="8" width="25.88"/>
+    <col customWidth="1" min="9" max="9" width="25.75"/>
+    <col customWidth="1" min="10" max="10" width="25.88"/>
+    <col customWidth="1" min="11" max="11" width="27.88"/>
+    <col customWidth="1" min="12" max="12" width="26.63"/>
+    <col customWidth="1" min="13" max="13" width="27.75"/>
+    <col customWidth="1" min="14" max="32" width="34.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1345,18 +1368,18 @@
       <c r="AD5" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AE5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF5" s="20" t="s">
-        <v>32</v>
+      <c r="AE5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF5" s="21" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -1443,11 +1466,11 @@
       <c r="AD6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AE6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF6" s="22" t="s">
-        <v>17</v>
+      <c r="AE6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -1751,7 +1774,7 @@
       <c r="B10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="28" t="s">
@@ -2102,8 +2125,8 @@
       <c r="U13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="11" t="s">
-        <v>14</v>
+      <c r="V13" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="W13" s="11" t="s">
         <v>13</v>
@@ -2440,7 +2463,7 @@
       <c r="C17" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="27" t="s">
@@ -2690,8 +2713,8 @@
       <c r="U19" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="V19" s="29" t="s">
-        <v>45</v>
+      <c r="V19" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="W19" s="29" t="s">
         <v>23</v>
@@ -3183,8 +3206,8 @@
       <c r="V24" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="W24" s="11" t="s">
-        <v>81</v>
+      <c r="W24" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="X24" s="11" t="s">
         <v>13</v>
@@ -3376,11 +3399,11 @@
       <c r="U26" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="V26" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="W26" s="11" t="s">
-        <v>23</v>
+      <c r="V26" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="W26" s="36" t="s">
+        <v>34</v>
       </c>
       <c r="X26" s="11" t="s">
         <v>23</v>
@@ -3949,11 +3972,11 @@
       <c r="P32" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="Q32" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="R32" s="11" t="s">
-        <v>45</v>
+      <c r="Q32" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="R32" s="12" t="s">
+        <v>93</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>17</v>
@@ -3974,7 +3997,7 @@
         <v>84</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Z32" s="11" t="s">
         <v>17</v>
@@ -4000,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>25</v>
@@ -4054,7 +4077,7 @@
         <v>17</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T33" s="11" t="s">
         <v>23</v>
@@ -4098,7 +4121,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>31</v>
@@ -4106,11 +4129,11 @@
       <c r="C34" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D34" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>97</v>
+      <c r="D34" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="F34" s="27" t="s">
         <v>14</v>
@@ -4195,13 +4218,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="s">
-        <v>98</v>
+      <c r="A35" s="38" t="s">
+        <v>99</v>
       </c>
       <c r="B35" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="39" t="s">
         <v>25</v>
       </c>
       <c r="D35" s="23" t="s">
@@ -4222,26 +4245,26 @@
       <c r="I35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J35" s="21" t="s">
+      <c r="J35" s="22" t="s">
         <v>21</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L35" s="39" t="s">
+      <c r="L35" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="M35" s="39" t="s">
+      <c r="M35" s="40" t="s">
         <v>12</v>
       </c>
       <c r="N35" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="O35" s="40" t="s">
+      <c r="O35" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="P35" s="39" t="s">
-        <v>99</v>
+      <c r="P35" s="40" t="s">
+        <v>100</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>20</v>
@@ -4249,7 +4272,7 @@
       <c r="R35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="S35" s="41" t="s">
+      <c r="S35" s="42" t="s">
         <v>45</v>
       </c>
       <c r="T35" s="29" t="s">
@@ -4273,10 +4296,10 @@
       <c r="Z35" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AA35" s="39" t="s">
+      <c r="AA35" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="AB35" s="39" t="s">
+      <c r="AB35" s="40" t="s">
         <v>12</v>
       </c>
       <c r="AC35" s="29" t="s">
@@ -4288,13 +4311,13 @@
       <c r="AE35" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="AF35" s="42" t="s">
+      <c r="AF35" s="43" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="s">
-        <v>100</v>
+      <c r="A36" s="38" t="s">
+        <v>101</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>17</v>
@@ -4326,10 +4349,10 @@
       <c r="K36" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="L36" s="39" t="s">
+      <c r="L36" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="M36" s="39" t="s">
+      <c r="M36" s="40" t="s">
         <v>40</v>
       </c>
       <c r="N36" s="23" t="s">
@@ -4371,10 +4394,10 @@
       <c r="Z36" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="AA36" s="39" t="s">
+      <c r="AA36" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AB36" s="39" t="s">
+      <c r="AB36" s="40" t="s">
         <v>19</v>
       </c>
       <c r="AC36" s="3" t="s">
@@ -4386,13 +4409,13 @@
       <c r="AE36" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="AF36" s="42" t="s">
+      <c r="AF36" s="43" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>17</v>
@@ -4412,7 +4435,7 @@
       <c r="G37" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="43" t="s">
+      <c r="H37" s="44" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="27" t="s">
@@ -4490,7 +4513,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -4588,16 +4611,16 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>34</v>
@@ -4677,7 +4700,7 @@
       <c r="AD39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE39" s="44" t="s">
+      <c r="AE39" s="45" t="s">
         <v>21</v>
       </c>
       <c r="AF39" s="3" t="s">
@@ -4686,7 +4709,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B40" s="29" t="s">
         <v>25</v>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="111">
   <si>
     <t>Viernes</t>
   </si>
@@ -196,6 +196,9 @@
     <t>16:00 - 21:00</t>
   </si>
   <si>
+    <t>14:00-22:00</t>
+  </si>
+  <si>
     <t>DAYANA ANDREA RAMIREZ BERNAL</t>
   </si>
   <si>
@@ -271,10 +274,16 @@
     <t>ANGIE CAROLINA NARANJO HERRERA</t>
   </si>
   <si>
+    <t xml:space="preserve">Incapacidad </t>
+  </si>
+  <si>
     <t>JHOSNMAN ARLEY RODRIGUEZ ARIAS</t>
   </si>
   <si>
     <t>13:00 - 18:00</t>
+  </si>
+  <si>
+    <t>incapacidad</t>
   </si>
   <si>
     <t>PAOLA STEFANIA ARIAS PEÑA</t>
@@ -344,7 +353,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -385,11 +394,6 @@
     <font>
       <sz val="8.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8.0"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -630,8 +634,8 @@
     <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -654,7 +658,7 @@
     <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2229,8 +2233,8 @@
       <c r="W14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="X14" s="11" t="s">
-        <v>54</v>
+      <c r="X14" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="Y14" s="11" t="s">
         <v>16</v>
@@ -2259,13 +2263,13 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>17</v>
@@ -2283,7 +2287,7 @@
         <v>45</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J15" s="27" t="s">
         <v>18</v>
@@ -2310,7 +2314,7 @@
         <v>16</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S15" s="11" t="s">
         <v>17</v>
@@ -2333,17 +2337,17 @@
       <c r="Y15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>16</v>
+      <c r="Z15" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA15" s="28" t="s">
+        <v>20</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>20</v>
+      <c r="AC15" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>20</v>
@@ -2357,7 +2361,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>25</v>
@@ -2366,7 +2370,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>54</v>
@@ -2429,7 +2433,7 @@
         <v>34</v>
       </c>
       <c r="Y16" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z16" s="3" t="s">
         <v>43</v>
@@ -2447,7 +2451,7 @@
         <v>54</v>
       </c>
       <c r="AE16" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF16" s="3" t="s">
         <v>16</v>
@@ -2455,13 +2459,13 @@
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>17</v>
@@ -2524,7 +2528,7 @@
         <v>34</v>
       </c>
       <c r="X17" s="11" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="Y17" s="11" t="s">
         <v>17</v>
@@ -2553,7 +2557,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>40</v>
@@ -2598,7 +2602,7 @@
         <v>49</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="11" t="s">
         <v>13</v>
@@ -2651,7 +2655,7 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>17</v>
@@ -2693,7 +2697,7 @@
         <v>14</v>
       </c>
       <c r="O19" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P19" s="29" t="s">
         <v>25</v>
@@ -2714,7 +2718,7 @@
         <v>45</v>
       </c>
       <c r="V19" s="31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W19" s="29" t="s">
         <v>23</v>
@@ -2726,7 +2730,7 @@
         <v>17</v>
       </c>
       <c r="Z19" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>17</v>
@@ -2749,7 +2753,7 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>23</v>
@@ -2761,7 +2765,7 @@
         <v>17</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" s="29" t="s">
         <v>44</v>
@@ -2815,7 +2819,7 @@
         <v>14</v>
       </c>
       <c r="W20" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X20" s="29" t="s">
         <v>18</v>
@@ -2847,7 +2851,7 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" s="29" t="s">
         <v>23</v>
@@ -2889,10 +2893,10 @@
         <v>43</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q21" s="11" t="s">
         <v>18</v>
@@ -2945,7 +2949,7 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>43</v>
@@ -2957,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="27" t="s">
         <v>23</v>
@@ -3002,7 +3006,7 @@
         <v>45</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U22" s="11" t="s">
         <v>16</v>
@@ -3043,7 +3047,7 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>23</v>
@@ -3061,7 +3065,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H23" s="27" t="s">
         <v>43</v>
@@ -3141,7 +3145,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="29" t="s">
         <v>23</v>
@@ -3153,13 +3157,13 @@
         <v>17</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F24" s="27" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H24" s="27" t="s">
         <v>45</v>
@@ -3195,7 +3199,7 @@
         <v>21</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T24" s="11" t="s">
         <v>16</v>
@@ -3239,7 +3243,7 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="29" t="s">
         <v>43</v>
@@ -3329,7 +3333,7 @@
         <v>45</v>
       </c>
       <c r="AE25" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF25" s="3" t="s">
         <v>17</v>
@@ -3337,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" s="29" t="s">
         <v>20</v>
@@ -3397,7 +3401,7 @@
         <v>34</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V26" s="12" t="s">
         <v>34</v>
@@ -3409,7 +3413,7 @@
         <v>23</v>
       </c>
       <c r="Y26" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>25</v>
@@ -3435,7 +3439,7 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="29" t="s">
         <v>44</v>
@@ -3486,7 +3490,7 @@
         <v>25</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S27" s="12" t="s">
         <v>17</v>
@@ -3500,8 +3504,8 @@
       <c r="V27" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="W27" s="11" t="s">
-        <v>23</v>
+      <c r="W27" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="X27" s="11" t="s">
         <v>23</v>
@@ -3510,7 +3514,7 @@
         <v>17</v>
       </c>
       <c r="Z27" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>22</v>
@@ -3533,7 +3537,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>23</v>
@@ -3557,7 +3561,7 @@
         <v>45</v>
       </c>
       <c r="I28" s="27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J28" s="27" t="s">
         <v>29</v>
@@ -3593,7 +3597,7 @@
         <v>49</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V28" s="11" t="s">
         <v>49</v>
@@ -3604,11 +3608,11 @@
       <c r="X28" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="Y28" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z28" s="3" t="s">
-        <v>23</v>
+      <c r="Y28" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z28" s="28" t="s">
+        <v>90</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>34</v>
@@ -3631,10 +3635,10 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>22</v>
@@ -3729,13 +3733,13 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="29" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>49</v>
@@ -3827,7 +3831,7 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B31" s="29" t="s">
         <v>23</v>
@@ -3860,7 +3864,7 @@
         <v>49</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M31" s="11" t="s">
         <v>29</v>
@@ -3910,14 +3914,14 @@
       <c r="AB31" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AC31" s="3" t="s">
+      <c r="AC31" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE31" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="AD31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE31" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AF31" s="3" t="s">
         <v>22</v>
@@ -3925,7 +3929,7 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>34</v>
@@ -3973,10 +3977,10 @@
         <v>45</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="R32" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>17</v>
@@ -3994,10 +3998,10 @@
         <v>23</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y32" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Z32" s="11" t="s">
         <v>17</v>
@@ -4023,7 +4027,7 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>25</v>
@@ -4077,7 +4081,7 @@
         <v>17</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="T33" s="11" t="s">
         <v>23</v>
@@ -4094,8 +4098,8 @@
       <c r="X33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="Y33" s="11" t="s">
-        <v>29</v>
+      <c r="Y33" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>16</v>
@@ -4121,7 +4125,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>31</v>
@@ -4130,22 +4134,22 @@
         <v>31</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F34" s="27" t="s">
         <v>14</v>
       </c>
       <c r="G34" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H34" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I34" s="32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J34" s="27" t="s">
         <v>13</v>
@@ -4157,7 +4161,7 @@
         <v>17</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N34" s="11" t="s">
         <v>23</v>
@@ -4211,7 +4215,7 @@
         <v>16</v>
       </c>
       <c r="AE34" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF34" s="3" t="s">
         <v>17</v>
@@ -4219,7 +4223,7 @@
     </row>
     <row r="35">
       <c r="A35" s="38" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B35" s="27" t="s">
         <v>17</v>
@@ -4264,7 +4268,7 @@
         <v>13</v>
       </c>
       <c r="P35" s="40" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>20</v>
@@ -4290,8 +4294,8 @@
       <c r="X35" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="Y35" s="29" t="s">
-        <v>23</v>
+      <c r="Y35" s="40" t="s">
+        <v>45</v>
       </c>
       <c r="Z35" s="23" t="s">
         <v>17</v>
@@ -4317,7 +4321,7 @@
     </row>
     <row r="36">
       <c r="A36" s="38" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>17</v>
@@ -4388,8 +4392,8 @@
       <c r="X36" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y36" s="3" t="s">
-        <v>20</v>
+      <c r="Y36" s="28" t="s">
+        <v>21</v>
       </c>
       <c r="Z36" s="23" t="s">
         <v>49</v>
@@ -4415,7 +4419,7 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>17</v>
@@ -4513,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -4552,7 +4556,7 @@
         <v>17</v>
       </c>
       <c r="N38" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O38" s="27" t="s">
         <v>23</v>
@@ -4564,7 +4568,7 @@
         <v>23</v>
       </c>
       <c r="R38" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S38" s="29" t="s">
         <v>17</v>
@@ -4611,16 +4615,16 @@
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>34</v>
@@ -4709,7 +4713,7 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B40" s="29" t="s">
         <v>25</v>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="84">
   <si>
     <t>Lunes</t>
   </si>
@@ -263,12 +263,6 @@
   </si>
   <si>
     <t>13:00 - 19:00</t>
-  </si>
-  <si>
-    <t>08:01 - 18:00</t>
-  </si>
-  <si>
-    <t>08:01 - 17:00</t>
   </si>
 </sst>
 </file>
@@ -332,7 +326,7 @@
       <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,6 +361,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF1A983"/>
         <bgColor rgb="FFF1A983"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -471,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -544,8 +544,8 @@
     <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -568,6 +568,9 @@
     <xf borderId="10" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf borderId="10" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf borderId="9" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -577,13 +580,16 @@
     <xf borderId="4" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="10" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -592,21 +598,42 @@
     <xf borderId="4" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="7" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf borderId="4" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="10" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -624,6 +651,9 @@
     </xf>
     <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1175,7 +1205,7 @@
       <c r="M4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="23" t="s">
+      <c r="N4" s="21" t="s">
         <v>18</v>
       </c>
       <c r="O4" s="2" t="s">
@@ -1256,7 +1286,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>13</v>
@@ -1267,11 +1297,11 @@
       <c r="L5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="11" t="s">
         <v>13</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>13</v>
@@ -1724,8 +1754,8 @@
       <c r="F10" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>12</v>
+      <c r="G10" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>16</v>
@@ -1813,7 +1843,7 @@
       <c r="D11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="33" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="31" t="s">
@@ -1825,7 +1855,7 @@
       <c r="H11" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="33" t="s">
+      <c r="I11" s="34" t="s">
         <v>16</v>
       </c>
       <c r="J11" s="10" t="s">
@@ -1855,7 +1885,7 @@
       <c r="R11" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="S11" s="34" t="s">
+      <c r="S11" s="35" t="s">
         <v>16</v>
       </c>
       <c r="T11" s="10" t="s">
@@ -2009,10 +2039,10 @@
       <c r="F13" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="35" t="s">
+      <c r="G13" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="37" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="9" t="s">
@@ -2092,10 +2122,10 @@
       <c r="B14" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="38" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="9" t="s">
@@ -2104,7 +2134,7 @@
       <c r="F14" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="38" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="9" t="s">
@@ -2146,26 +2176,26 @@
       <c r="T14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="U14" s="37" t="s">
+      <c r="U14" s="39" t="s">
         <v>47</v>
       </c>
       <c r="V14" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="W14" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="X14" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y14" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z14" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA14" s="10" t="s">
-        <v>40</v>
+      <c r="W14" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="X14" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y14" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z14" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA14" s="41" t="s">
+        <v>38</v>
       </c>
       <c r="AB14" s="10" t="s">
         <v>16</v>
@@ -2199,7 +2229,7 @@
       <c r="F15" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="37" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -2288,13 +2318,13 @@
       <c r="D16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>18</v>
+      <c r="E16" s="42" t="s">
+        <v>26</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="37" t="s">
         <v>17</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -2377,7 +2407,7 @@
       <c r="B17" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="38" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="30" t="s">
@@ -2398,7 +2428,7 @@
       <c r="I17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="31" t="s">
+      <c r="J17" s="22" t="s">
         <v>47</v>
       </c>
       <c r="K17" s="31" t="s">
@@ -2425,10 +2455,10 @@
       <c r="R17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S17" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" s="40" t="s">
+      <c r="S17" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="T17" s="43" t="s">
         <v>18</v>
       </c>
       <c r="U17" s="10" t="s">
@@ -2443,14 +2473,14 @@
       <c r="X17" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="Y17" s="38" t="s">
+      <c r="Y17" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="Z17" s="39" t="s">
+      <c r="Z17" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="AA17" s="39" t="s">
-        <v>38</v>
+      <c r="AA17" s="44" t="s">
+        <v>40</v>
       </c>
       <c r="AB17" s="10" t="s">
         <v>16</v>
@@ -2481,13 +2511,13 @@
       <c r="E18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="45" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="46" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="9" t="s">
@@ -2502,7 +2532,7 @@
       <c r="L18" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M18" s="43" t="s">
+      <c r="M18" s="47" t="s">
         <v>16</v>
       </c>
       <c r="N18" s="10" t="s">
@@ -2588,13 +2618,13 @@
       <c r="I19" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>33</v>
+      <c r="J19" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="48" t="s">
         <v>33</v>
       </c>
       <c r="M19" s="9" t="s">
@@ -2680,26 +2710,26 @@
       <c r="H20" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="35" t="s">
+      <c r="I20" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K20" s="9" t="s">
+      <c r="L20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L20" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>47</v>
-      </c>
       <c r="N20" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="25" t="s">
-        <v>9</v>
+        <v>46</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="P20" s="31" t="s">
         <v>18</v>
@@ -2722,7 +2752,7 @@
       <c r="V20" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="W20" s="35" t="s">
+      <c r="W20" s="37" t="s">
         <v>46</v>
       </c>
       <c r="X20" s="9" t="s">
@@ -2754,62 +2784,62 @@
       <c r="A21" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>18</v>
+      <c r="B21" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>15</v>
       </c>
       <c r="H21" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="O21" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q21" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="R21" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="S21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="T21" s="31" t="s">
-        <v>18</v>
+      <c r="I21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="M21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="N21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="P21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="R21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="S21" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="T21" s="50" t="s">
+        <v>15</v>
       </c>
       <c r="U21" s="31" t="s">
         <v>17</v>
@@ -2817,7 +2847,7 @@
       <c r="V21" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="W21" s="35" t="s">
+      <c r="W21" s="37" t="s">
         <v>47</v>
       </c>
       <c r="X21" s="9" t="s">
@@ -2856,13 +2886,13 @@
         <v>33</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>12</v>
       </c>
       <c r="G22" s="31" t="s">
         <v>38</v>
@@ -2965,23 +2995,23 @@
       <c r="H23" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="I23" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>46</v>
+      <c r="I23" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="O23" s="11" t="s">
         <v>16</v>
@@ -3007,7 +3037,7 @@
       <c r="V23" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="W23" s="35" t="s">
+      <c r="W23" s="37" t="s">
         <v>33</v>
       </c>
       <c r="X23" s="9" t="s">
@@ -3025,7 +3055,7 @@
       <c r="AB23" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AC23" s="44" t="s">
+      <c r="AC23" s="51" t="s">
         <v>16</v>
       </c>
       <c r="AD23" s="27" t="s">
@@ -3051,7 +3081,7 @@
       <c r="E24" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="45" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="27" t="s">
@@ -3060,14 +3090,14 @@
       <c r="H24" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I24" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>9</v>
+      <c r="I24" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="L24" s="9" t="s">
         <v>30</v>
@@ -3143,7 +3173,7 @@
       <c r="D25" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="E25" s="54" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="31" t="s">
@@ -3250,7 +3280,7 @@
       <c r="H26" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="35" t="s">
+      <c r="I26" s="37" t="s">
         <v>27</v>
       </c>
       <c r="J26" s="9" t="s">
@@ -3289,10 +3319,10 @@
       <c r="U26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V26" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="W26" s="46" t="s">
+      <c r="V26" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="W26" s="55" t="s">
         <v>16</v>
       </c>
       <c r="X26" s="30" t="s">
@@ -3333,13 +3363,13 @@
       <c r="D27" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="54" t="s">
         <v>47</v>
       </c>
       <c r="F27" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="37" t="s">
         <v>16</v>
       </c>
       <c r="H27" s="9" t="s">
@@ -3363,7 +3393,7 @@
       <c r="N27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="O27" s="47" t="s">
+      <c r="O27" s="56" t="s">
         <v>27</v>
       </c>
       <c r="P27" s="29" t="s">
@@ -3428,7 +3458,7 @@
       <c r="D28" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="45" t="s">
+      <c r="E28" s="54" t="s">
         <v>12</v>
       </c>
       <c r="F28" s="31" t="s">
@@ -3437,7 +3467,7 @@
       <c r="G28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="37" t="s">
         <v>16</v>
       </c>
       <c r="I28" s="10" t="s">
@@ -3446,8 +3476,8 @@
       <c r="J28" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="K28" s="10" t="s">
-        <v>18</v>
+      <c r="K28" s="53" t="s">
+        <v>9</v>
       </c>
       <c r="L28" s="10" t="s">
         <v>18</v>
@@ -3461,7 +3491,7 @@
       <c r="O28" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="P28" s="35" t="s">
+      <c r="P28" s="37" t="s">
         <v>16</v>
       </c>
       <c r="Q28" s="30" t="s">
@@ -3523,7 +3553,7 @@
       <c r="D29" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="54" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="31" t="s">
@@ -3538,7 +3568,7 @@
       <c r="I29" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="J29" s="35" t="s">
+      <c r="J29" s="37" t="s">
         <v>30</v>
       </c>
       <c r="K29" s="9" t="s">
@@ -3615,14 +3645,14 @@
       <c r="C30" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>38</v>
+      <c r="D30" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>12</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>38</v>
@@ -3630,26 +3660,26 @@
       <c r="H30" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>17</v>
+      <c r="I30" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N30" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="O30" s="11" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" s="25" t="s">
+        <v>9</v>
       </c>
       <c r="P30" s="31" t="s">
         <v>47</v>
@@ -3713,16 +3743,16 @@
       <c r="D31" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" s="57" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="H31" s="42" t="s">
+      <c r="H31" s="46" t="s">
         <v>16</v>
       </c>
       <c r="I31" s="9" t="s">
@@ -3758,10 +3788,10 @@
       <c r="S31" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="T31" s="43" t="s">
+      <c r="T31" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="U31" s="43" t="s">
+      <c r="U31" s="47" t="s">
         <v>18</v>
       </c>
       <c r="V31" s="10" t="s">
@@ -3782,10 +3812,10 @@
       <c r="AA31" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="AB31" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="50" t="s">
+      <c r="AB31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="59" t="s">
         <v>46</v>
       </c>
       <c r="AD31" s="10" t="s">
@@ -3918,10 +3948,10 @@
       <c r="I33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J33" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K33" s="9" t="s">
+      <c r="J33" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="K33" s="48" t="s">
         <v>10</v>
       </c>
       <c r="L33" s="9" t="s">
@@ -4013,8 +4043,8 @@
       <c r="I34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J34" s="2" t="s">
-        <v>9</v>
+      <c r="J34" s="60" t="s">
+        <v>47</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>9</v>
@@ -4031,7 +4061,7 @@
       <c r="O34" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="P34" s="42" t="s">
+      <c r="P34" s="46" t="s">
         <v>40</v>
       </c>
       <c r="Q34" s="30" t="s">
@@ -4099,37 +4129,37 @@
       <c r="F35" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="35" t="s">
+      <c r="G35" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="42" t="s">
+      <c r="I35" s="46" t="s">
         <v>32</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K35" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="N35" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="O35" s="42" t="s">
+      <c r="K35" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="M35" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="46" t="s">
         <v>16</v>
       </c>
       <c r="P35" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="Q35" s="42" t="s">
+      <c r="Q35" s="46" t="s">
         <v>17</v>
       </c>
       <c r="R35" s="10" t="s">
@@ -4147,19 +4177,19 @@
       <c r="V35" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="W35" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="X35" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y35" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z35" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA35" s="42" t="s">
+      <c r="W35" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="X35" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y35" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z35" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA35" s="46" t="s">
         <v>17</v>
       </c>
       <c r="AB35" s="2" t="s">
@@ -4194,28 +4224,28 @@
       <c r="F36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G36" s="42" t="s">
+      <c r="G36" s="46" t="s">
         <v>16</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="L36" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="M36" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="N36" s="42" t="s">
+      <c r="I36" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="L36" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="46" t="s">
         <v>17</v>
       </c>
       <c r="O36" s="25" t="s">
@@ -4304,7 +4334,7 @@
       <c r="K37" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L37" s="42" t="s">
+      <c r="L37" s="46" t="s">
         <v>16</v>
       </c>
       <c r="M37" s="2" t="s">
@@ -4363,190 +4393,6 @@
       </c>
       <c r="AE37" s="30" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="L38" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="M38" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="N38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="R38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="S38" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="T38" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="U38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="V38" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="W38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="X38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y38" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z38" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA38" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC38" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD38" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE38" s="42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="J39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="K39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="L39" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="M39" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="N39" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="R39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="S39" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="T39" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="U39" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="V39" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="W39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="X39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y39" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z39" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA39" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB39" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC39" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD39" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE39" s="42" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29303"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97597A3F-5845-4CB5-BDA1-B229B937C9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E04E8F35-ED9D-42C9-9198-FE8F93DAA43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="87">
   <si>
     <t>Lunes</t>
   </si>
@@ -96,91 +96,94 @@
     <t>10:00 - 16:00</t>
   </si>
   <si>
+    <t>21:00 - 6:00</t>
+  </si>
+  <si>
+    <t>22:00 - 6:00</t>
+  </si>
+  <si>
+    <t>JOSE GUILLERMO LOZANO GUERRA</t>
+  </si>
+  <si>
+    <t>Salario Emocional</t>
+  </si>
+  <si>
+    <t>16:00 - 22:00</t>
+  </si>
+  <si>
+    <t>13:00 - 21:00</t>
+  </si>
+  <si>
+    <t>11:00 - 17:00</t>
+  </si>
+  <si>
+    <t>JURANI ROSAS</t>
+  </si>
+  <si>
+    <t>JHON HENRY MARIN SANTOFIMIO</t>
+  </si>
+  <si>
+    <t>9:00 - 16:00</t>
+  </si>
+  <si>
     <t>6:00 - 12:00</t>
   </si>
   <si>
-    <t>21:00 - 6:00</t>
-  </si>
-  <si>
-    <t>22:00 - 6:00</t>
-  </si>
-  <si>
-    <t>JOSE GUILLERMO LOZANO GUERRA</t>
-  </si>
-  <si>
-    <t>Salario Emocional</t>
-  </si>
-  <si>
-    <t>16:00 - 22:00</t>
-  </si>
-  <si>
-    <t>13:00 - 21:00</t>
-  </si>
-  <si>
-    <t>JURANI ROSAS</t>
-  </si>
-  <si>
-    <t>JHON HENRY MARIN SANTOFIMIO</t>
-  </si>
-  <si>
-    <t>9:00 - 16:00</t>
-  </si>
-  <si>
     <t>NATALIA CARRILLO HERNANDEZ</t>
   </si>
   <si>
     <t>14:00 - 21:00</t>
   </si>
   <si>
+    <t>17:00 - 22:00</t>
+  </si>
+  <si>
+    <t>13:00 - 22:00</t>
+  </si>
+  <si>
+    <t>9:00 - 15:00</t>
+  </si>
+  <si>
+    <t>FABER SEBASTIAN FÚQUENE HERNANDEZ</t>
+  </si>
+  <si>
+    <t>8:00 - 14:00</t>
+  </si>
+  <si>
+    <t>FREDY ALEXANDER CALCETERO PARDO</t>
+  </si>
+  <si>
+    <t>15:00 - 21:00</t>
+  </si>
+  <si>
+    <t>8:00 - 13:00</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID CHAPARRO VARGAS</t>
+  </si>
+  <si>
+    <t>12:00 - 21:00</t>
+  </si>
+  <si>
+    <t>14:00 - 20:00</t>
+  </si>
+  <si>
+    <t>LOREN YIRETH INDABURO VARGAS</t>
+  </si>
+  <si>
+    <t>7:00 - 14:00</t>
+  </si>
+  <si>
+    <t>7:00 - 15:00</t>
+  </si>
+  <si>
+    <t>Novedad</t>
+  </si>
+  <si>
+    <t>JUAN DAVID ORJUELA MORALES</t>
+  </si>
+  <si>
     <t>8:00 - 15:00</t>
-  </si>
-  <si>
-    <t>17:00 - 22:00</t>
-  </si>
-  <si>
-    <t>13:00 - 22:00</t>
-  </si>
-  <si>
-    <t>9:00 - 15:00</t>
-  </si>
-  <si>
-    <t>FABER SEBASTIAN FÚQUENE HERNANDEZ</t>
-  </si>
-  <si>
-    <t>8:00 - 14:00</t>
-  </si>
-  <si>
-    <t>FREDY ALEXANDER CALCETERO PARDO</t>
-  </si>
-  <si>
-    <t>15:00 - 21:00</t>
-  </si>
-  <si>
-    <t>8:00 - 13:00</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID CHAPARRO VARGAS</t>
-  </si>
-  <si>
-    <t>12:00 - 21:00</t>
-  </si>
-  <si>
-    <t>14:00 - 20:00</t>
-  </si>
-  <si>
-    <t>LOREN YIRETH INDABURO VARGAS</t>
-  </si>
-  <si>
-    <t>7:00 - 14:00</t>
-  </si>
-  <si>
-    <t>7:00 - 15:00</t>
-  </si>
-  <si>
-    <t>Novedad</t>
-  </si>
-  <si>
-    <t>JUAN DAVID ORJUELA MORALES</t>
   </si>
   <si>
     <t>7:00 - 13:00</t>
@@ -667,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -792,9 +795,6 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
@@ -836,6 +836,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1422,40 +1434,40 @@
       <c r="V4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="28" t="s">
+      <c r="W4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="X4" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB4" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC4" s="28" t="s">
-        <v>22</v>
-      </c>
       <c r="AD4" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="12.75">
       <c r="A5" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>25</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>9</v>
@@ -1497,16 +1509,16 @@
         <v>13</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q5" s="23" t="s">
         <v>18</v>
       </c>
       <c r="R5" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="T5" s="23" t="s">
         <v>18</v>
@@ -1515,16 +1527,16 @@
         <v>16</v>
       </c>
       <c r="V5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="W5" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="X5" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="W5" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="X5" s="27" t="s">
-        <v>10</v>
-      </c>
       <c r="Y5" s="27" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Z5" s="27" t="s">
         <v>10</v>
@@ -1535,8 +1547,8 @@
       <c r="AB5" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="AC5" s="19" t="s">
-        <v>16</v>
+      <c r="AC5" s="60" t="s">
+        <v>13</v>
       </c>
       <c r="AD5" s="25" t="s">
         <v>18</v>
@@ -1550,85 +1562,85 @@
         <v>28</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="19" t="s">
         <v>16</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M6" s="19" t="s">
         <v>16</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U6" s="19" t="s">
         <v>16</v>
       </c>
       <c r="V6" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB6" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC6" s="19" t="s">
         <v>16</v>
@@ -1651,7 +1663,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>16</v>
@@ -1660,10 +1672,10 @@
         <v>18</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>30</v>
@@ -1684,19 +1696,19 @@
         <v>16</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P7" s="28" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="Q7" s="28" t="s">
         <v>9</v>
       </c>
       <c r="R7" s="28" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="S7" s="28" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="T7" s="28" t="s">
         <v>9</v>
@@ -1708,25 +1720,25 @@
         <v>16</v>
       </c>
       <c r="W7" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="X7" s="25" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+      <c r="X7" s="42" t="s">
+        <v>16</v>
       </c>
       <c r="Y7" s="25" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Z7" s="25" t="s">
         <v>18</v>
       </c>
       <c r="AA7" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB7" s="19" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="AB7" s="61" t="s">
+        <v>18</v>
       </c>
       <c r="AC7" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD7" s="30" t="s">
         <v>9</v>
@@ -1737,7 +1749,7 @@
     </row>
     <row r="8" spans="1:31" ht="12.75">
       <c r="A8" s="17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>30</v>
@@ -1779,13 +1791,13 @@
         <v>16</v>
       </c>
       <c r="O8" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P8" s="34" t="s">
         <v>12</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="R8" s="34" t="s">
         <v>12</v>
@@ -1835,82 +1847,82 @@
         <v>37</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O9" s="19" t="s">
         <v>16</v>
       </c>
       <c r="P9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S9" s="19" t="s">
         <v>16</v>
       </c>
       <c r="T9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V9" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA9" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB9" s="19" t="s">
         <v>16</v>
@@ -1975,10 +1987,10 @@
         <v>18</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S10" s="35" t="s">
         <v>16</v>
@@ -1996,22 +2008,22 @@
         <v>16</v>
       </c>
       <c r="X10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA10" s="34" t="s">
         <v>40</v>
       </c>
       <c r="AB10" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AC10" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AD10" s="34" t="s">
         <v>9</v>
@@ -2028,37 +2040,37 @@
         <v>17</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I11" s="39" t="s">
         <v>16</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K11" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L11" s="35" t="s">
         <v>44</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N11" s="35" t="s">
         <v>18</v>
@@ -2079,13 +2091,13 @@
         <v>16</v>
       </c>
       <c r="T11" s="35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U11" s="35" t="s">
         <v>17</v>
       </c>
       <c r="V11" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W11" s="34" t="s">
         <v>30</v>
@@ -2161,35 +2173,35 @@
       <c r="O12" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="R12" s="41" t="s">
+      <c r="P12" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="R12" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="S12" s="41" t="s">
+      <c r="S12" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="T12" s="41" t="s">
+      <c r="T12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="U12" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="V12" s="41" t="s">
+      <c r="U12" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="V12" s="26" t="s">
         <v>16</v>
       </c>
       <c r="W12" s="35" t="s">
         <v>17</v>
       </c>
       <c r="X12" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y12" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z12" s="35" t="s">
         <v>17</v>
@@ -2204,10 +2216,10 @@
         <v>16</v>
       </c>
       <c r="AD12" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE12" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="12.75">
@@ -2230,7 +2242,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="42" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="H13" s="31" t="s">
         <v>16</v>
@@ -2251,37 +2263,37 @@
         <v>9</v>
       </c>
       <c r="N13" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="O13" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="P13" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q13" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="R13" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="S13" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="T13" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="U13" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="V13" s="44" t="s">
+      <c r="R13" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="S13" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="U13" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="V13" s="35" t="s">
         <v>40</v>
       </c>
       <c r="W13" s="35" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="X13" s="35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y13" s="34" t="s">
         <v>13</v>
@@ -2299,15 +2311,15 @@
         <v>16</v>
       </c>
       <c r="AD13" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE13" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="12.75">
       <c r="A14" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>46</v>
@@ -2319,7 +2331,7 @@
         <v>46</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" s="24" t="s">
         <v>46</v>
@@ -2331,13 +2343,13 @@
         <v>16</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K14" s="45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L14" s="35" t="s">
         <v>16</v>
@@ -2349,78 +2361,78 @@
         <v>18</v>
       </c>
       <c r="O14" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q14" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="S14" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="T14" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="U14" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="R14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="S14" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="U14" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="V14" s="41" t="s">
+      <c r="V14" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="W14" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="X14" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y14" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z14" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA14" s="48" t="s">
+      <c r="W14" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="X14" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y14" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z14" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA14" s="47" t="s">
         <v>38</v>
       </c>
       <c r="AB14" s="35" t="s">
         <v>16</v>
       </c>
       <c r="AC14" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AD14" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE14" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="12.75">
       <c r="A15" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F15" s="26" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H15" s="31" t="s">
         <v>16</v>
@@ -2429,13 +2441,13 @@
         <v>36</v>
       </c>
       <c r="J15" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M15" s="35" t="s">
         <v>12</v>
@@ -2443,32 +2455,32 @@
       <c r="N15" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="O15" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="P15" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q15" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="R15" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="S15" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="T15" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="U15" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="V15" s="44" t="s">
+      <c r="O15" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="P15" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="R15" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="S15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="U15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="35" t="s">
         <v>16</v>
       </c>
       <c r="W15" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X15" s="35" t="s">
         <v>30</v>
@@ -2489,7 +2501,7 @@
         <v>12</v>
       </c>
       <c r="AD15" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE15" s="19" t="s">
         <v>18</v>
@@ -2497,7 +2509,7 @@
     </row>
     <row r="16" spans="1:31" ht="12.75">
       <c r="A16" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>17</v>
@@ -2509,7 +2521,7 @@
         <v>18</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="26" t="s">
         <v>18</v>
@@ -2541,25 +2553,25 @@
       <c r="O16" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="P16" s="43" t="s">
+      <c r="P16" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Q16" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="R16" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="S16" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="T16" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="U16" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="V16" s="44" t="s">
+      <c r="Q16" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="T16" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="U16" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="V16" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W16" s="34" t="s">
@@ -2569,7 +2581,7 @@
         <v>16</v>
       </c>
       <c r="Y16" s="34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z16" s="34" t="s">
         <v>30</v>
@@ -2581,7 +2593,7 @@
         <v>30</v>
       </c>
       <c r="AC16" s="34" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="AD16" s="34" t="s">
         <v>18</v>
@@ -2592,15 +2604,15 @@
     </row>
     <row r="17" spans="1:31" ht="12.75">
       <c r="A17" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="49" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="24" t="s">
@@ -2631,31 +2643,31 @@
         <v>46</v>
       </c>
       <c r="N17" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O17" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="R17" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="S17" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" s="45" t="s">
+      <c r="P17" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q17" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="R17" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="S17" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="T17" s="63" t="s">
         <v>18</v>
       </c>
       <c r="U17" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="V17" s="44" t="s">
-        <v>32</v>
+        <v>44</v>
+      </c>
+      <c r="V17" s="35" t="s">
+        <v>44</v>
       </c>
       <c r="W17" s="26" t="s">
         <v>16</v>
@@ -2663,31 +2675,31 @@
       <c r="X17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="Y17" s="47" t="s">
+      <c r="Y17" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="Z17" s="47" t="s">
+      <c r="Z17" s="46" t="s">
         <v>38</v>
       </c>
       <c r="AA17" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="AB17" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC17" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD17" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE17" s="26" t="s">
-        <v>23</v>
+      <c r="AB17" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC17" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD17" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE17" s="34" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="12.75">
       <c r="A18" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>47</v>
@@ -2695,19 +2707,19 @@
       <c r="C18" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="D18" s="49" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="31" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="58" t="s">
+      <c r="H18" s="57" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="31" t="s">
@@ -2734,11 +2746,11 @@
       <c r="P18" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="Q18" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="R18" s="35" t="s">
-        <v>16</v>
+      <c r="Q18" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="R18" s="41" t="s">
+        <v>15</v>
       </c>
       <c r="S18" s="35" t="s">
         <v>17</v>
@@ -2746,11 +2758,11 @@
       <c r="T18" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="U18" s="34" t="s">
+      <c r="U18" s="43" t="s">
         <v>38</v>
       </c>
       <c r="V18" s="35" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="W18" s="34" t="s">
         <v>9</v>
@@ -2782,7 +2794,7 @@
     </row>
     <row r="19" spans="1:31" ht="12.75">
       <c r="A19" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>38</v>
@@ -2812,37 +2824,37 @@
         <v>12</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="L19" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="M19" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="N19" s="31" t="s">
         <v>10</v>
       </c>
       <c r="O19" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="P19" s="43" t="s">
         <v>35</v>
       </c>
       <c r="Q19" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R19" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S19" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T19" s="34" t="s">
         <v>17</v>
       </c>
       <c r="U19" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V19" s="35" t="s">
         <v>16</v>
@@ -2877,7 +2889,7 @@
     </row>
     <row r="20" spans="1:31" ht="12.75">
       <c r="A20" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>18</v>
@@ -2907,7 +2919,7 @@
         <v>17</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="L20" s="37" t="s">
         <v>47</v>
@@ -2931,13 +2943,13 @@
         <v>18</v>
       </c>
       <c r="S20" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T20" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U20" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V20" s="26" t="s">
         <v>16</v>
@@ -2967,12 +2979,12 @@
         <v>18</v>
       </c>
       <c r="AE20" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="12.75">
       <c r="A21" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>15</v>
@@ -3022,61 +3034,61 @@
       <c r="Q21" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="R21" s="41" t="s">
+      <c r="R21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="S21" s="41" t="s">
+      <c r="S21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="T21" s="41" t="s">
+      <c r="T21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="U21" s="41" t="s">
+      <c r="U21" s="26" t="s">
         <v>15</v>
       </c>
       <c r="V21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="W21" s="41" t="s">
+      <c r="W21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="41" t="s">
+      <c r="X21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="Y21" s="41" t="s">
+      <c r="Y21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="Z21" s="41" t="s">
+      <c r="Z21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="AA21" s="41" t="s">
+      <c r="AA21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="AB21" s="41" t="s">
+      <c r="AB21" s="31" t="s">
         <v>15</v>
       </c>
       <c r="AC21" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="AD21" s="41" t="s">
+      <c r="AD21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AE21" s="41" t="s">
+      <c r="AE21" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="12.75">
       <c r="A22" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>18</v>
@@ -3127,7 +3139,7 @@
         <v>46</v>
       </c>
       <c r="U22" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V22" s="26" t="s">
         <v>16</v>
@@ -3162,7 +3174,7 @@
     </row>
     <row r="23" spans="1:31" ht="12.75">
       <c r="A23" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>17</v>
@@ -3182,28 +3194,28 @@
       <c r="G23" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="H23" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="I23" s="52" t="s">
+      <c r="I23" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="M23" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="N23" s="53" t="s">
+      <c r="J23" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="M23" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="O23" s="53" t="s">
+      <c r="O23" s="52" t="s">
         <v>16</v>
       </c>
       <c r="P23" s="26" t="s">
@@ -3222,13 +3234,13 @@
         <v>18</v>
       </c>
       <c r="U23" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V23" s="26" t="s">
         <v>16</v>
       </c>
       <c r="W23" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="X23" s="31" t="s">
         <v>47</v>
@@ -3245,7 +3257,7 @@
       <c r="AB23" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="AC23" s="54" t="s">
+      <c r="AC23" s="53" t="s">
         <v>16</v>
       </c>
       <c r="AD23" s="26" t="s">
@@ -3257,7 +3269,7 @@
     </row>
     <row r="24" spans="1:31" ht="12.75">
       <c r="A24" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>17</v>
@@ -3275,7 +3287,7 @@
         <v>18</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H24" s="26" t="s">
         <v>16</v>
@@ -3284,10 +3296,10 @@
         <v>16</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L24" s="31" t="s">
         <v>30</v>
@@ -3352,28 +3364,28 @@
     </row>
     <row r="25" spans="1:31" ht="12.75">
       <c r="A25" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I25" s="26" t="s">
         <v>9</v>
@@ -3397,34 +3409,34 @@
         <v>16</v>
       </c>
       <c r="P25" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q25" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R25" s="26" t="s">
         <v>16</v>
       </c>
       <c r="S25" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T25" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U25" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V25" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W25" s="26" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="X25" s="26" t="s">
         <v>16</v>
       </c>
       <c r="Y25" s="26" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Z25" s="26" t="s">
         <v>9</v>
@@ -3439,7 +3451,7 @@
         <v>9</v>
       </c>
       <c r="AD25" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE25" s="26" t="s">
         <v>16</v>
@@ -3447,7 +3459,7 @@
     </row>
     <row r="26" spans="1:31" ht="12.75">
       <c r="A26" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>17</v>
@@ -3458,10 +3470,10 @@
       <c r="D26" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="55" t="s">
+      <c r="E26" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="54" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="26" t="s">
@@ -3471,7 +3483,7 @@
         <v>16</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J26" s="31" t="s">
         <v>40</v>
@@ -3480,7 +3492,7 @@
         <v>17</v>
       </c>
       <c r="L26" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M26" s="31" t="s">
         <v>17</v>
@@ -3492,7 +3504,7 @@
         <v>16</v>
       </c>
       <c r="P26" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q26" s="34" t="s">
         <v>18</v>
@@ -3504,10 +3516,10 @@
         <v>12</v>
       </c>
       <c r="T26" s="35" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="U26" s="35" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="V26" s="40" t="s">
         <v>16</v>
@@ -3528,7 +3540,7 @@
         <v>34</v>
       </c>
       <c r="AB26" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC26" s="34" t="s">
         <v>18</v>
@@ -3542,13 +3554,13 @@
     </row>
     <row r="27" spans="1:31" ht="12.75">
       <c r="A27" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>47</v>
@@ -3575,16 +3587,16 @@
         <v>17</v>
       </c>
       <c r="L27" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M27" s="31" t="s">
         <v>17</v>
       </c>
       <c r="N27" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="O27" s="56" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="O27" s="55" t="s">
+        <v>26</v>
       </c>
       <c r="P27" s="34" t="s">
         <v>12</v>
@@ -3605,39 +3617,39 @@
         <v>18</v>
       </c>
       <c r="V27" s="34" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="W27" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X27" s="34" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="Y27" s="34" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="Z27" s="34" t="s">
         <v>38</v>
       </c>
       <c r="AA27" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB27" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC27" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD27" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE27" s="34" t="s">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="AB27" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC27" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD27" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE27" s="26" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="12.75">
       <c r="A28" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>36</v>
@@ -3664,22 +3676,22 @@
         <v>18</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K28" s="37" t="s">
         <v>9</v>
       </c>
       <c r="L28" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M28" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="N28" s="49" t="s">
+      <c r="N28" s="48" t="s">
         <v>16</v>
       </c>
       <c r="O28" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P28" s="31" t="s">
         <v>16</v>
@@ -3687,7 +3699,7 @@
       <c r="Q28" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="R28" s="49" t="s">
+      <c r="R28" s="48" t="s">
         <v>13</v>
       </c>
       <c r="S28" s="35" t="s">
@@ -3706,7 +3718,7 @@
         <v>16</v>
       </c>
       <c r="X28" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y28" s="34" t="s">
         <v>35</v>
@@ -3718,10 +3730,10 @@
         <v>35</v>
       </c>
       <c r="AB28" s="34" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="AC28" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AD28" s="34" t="s">
         <v>18</v>
@@ -3732,7 +3744,7 @@
     </row>
     <row r="29" spans="1:31" ht="12.75">
       <c r="A29" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>18</v>
@@ -3744,16 +3756,16 @@
         <v>17</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="50" t="s">
-        <v>27</v>
+      <c r="G29" s="49" t="s">
+        <v>26</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="32" t="s">
         <v>46</v>
@@ -3786,16 +3798,16 @@
         <v>18</v>
       </c>
       <c r="S29" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T29" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U29" s="35" t="s">
         <v>18</v>
       </c>
       <c r="V29" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W29" s="35" t="s">
         <v>18</v>
@@ -3827,16 +3839,16 @@
     </row>
     <row r="30" spans="1:31" ht="12.75">
       <c r="A30" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>38</v>
@@ -3851,40 +3863,40 @@
         <v>16</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="K30" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="57" t="s">
+      <c r="L30" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M30" s="37" t="s">
         <v>47</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="O30" s="52" t="s">
         <v>9</v>
       </c>
       <c r="P30" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q30" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R30" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S30" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T30" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U30" s="26" t="s">
         <v>38</v>
@@ -3896,10 +3908,10 @@
         <v>18</v>
       </c>
       <c r="X30" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y30" s="35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z30" s="35" t="s">
         <v>17</v>
@@ -3911,7 +3923,7 @@
         <v>13</v>
       </c>
       <c r="AC30" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AD30" s="26" t="s">
         <v>46</v>
@@ -3922,7 +3934,7 @@
     </row>
     <row r="31" spans="1:31" ht="12.75">
       <c r="A31" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B31" s="42" t="s">
         <v>9</v>
@@ -3936,17 +3948,17 @@
       <c r="E31" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="49" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H31" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="57" t="s">
         <v>16</v>
       </c>
       <c r="I31" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J31" s="35" t="s">
         <v>18</v>
@@ -3979,7 +3991,7 @@
         <v>17</v>
       </c>
       <c r="T31" s="39" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="U31" s="39" t="s">
         <v>18</v>
@@ -4002,10 +4014,10 @@
       <c r="AA31" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AB31" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="59" t="s">
+      <c r="AB31" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="58" t="s">
         <v>46</v>
       </c>
       <c r="AD31" s="35" t="s">
@@ -4017,88 +4029,88 @@
     </row>
     <row r="32" spans="1:31" ht="12.75">
       <c r="A32" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N32" s="19" t="s">
         <v>16</v>
       </c>
       <c r="O32" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V32" s="19" t="s">
         <v>16</v>
       </c>
       <c r="W32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB32" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC32" s="19" t="s">
         <v>16</v>
@@ -4112,7 +4124,7 @@
     </row>
     <row r="33" spans="1:31" ht="12.75">
       <c r="A33" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>17</v>
@@ -4142,19 +4154,19 @@
         <v>12</v>
       </c>
       <c r="K33" s="31" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L33" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="M33" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="N33" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="N33" s="48" t="s">
         <v>16</v>
       </c>
       <c r="O33" s="31" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="P33" s="34" t="s">
         <v>12</v>
@@ -4175,7 +4187,7 @@
         <v>16</v>
       </c>
       <c r="V33" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W33" s="19" t="s">
         <v>9</v>
@@ -4184,16 +4196,16 @@
         <v>9</v>
       </c>
       <c r="Y33" s="34" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="Z33" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA33" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA33" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="AB33" s="49" t="s">
-        <v>79</v>
+      <c r="AB33" s="48" t="s">
+        <v>80</v>
       </c>
       <c r="AC33" s="34" t="s">
         <v>16</v>
@@ -4207,13 +4219,13 @@
     </row>
     <row r="34" spans="1:31" ht="12.75">
       <c r="A34" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>16</v>
@@ -4222,13 +4234,13 @@
         <v>16</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I34" s="19" t="s">
         <v>9</v>
@@ -4251,17 +4263,17 @@
       <c r="O34" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="P34" s="60" t="s">
+      <c r="P34" s="59" t="s">
         <v>40</v>
       </c>
       <c r="Q34" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R34" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S34" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T34" s="19" t="s">
         <v>18</v>
@@ -4270,7 +4282,7 @@
         <v>16</v>
       </c>
       <c r="V34" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W34" s="19" t="s">
         <v>16</v>
@@ -4279,13 +4291,13 @@
         <v>40</v>
       </c>
       <c r="Y34" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z34" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA34" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AB34" s="19" t="s">
         <v>9</v>
@@ -4294,24 +4306,24 @@
         <v>9</v>
       </c>
       <c r="AD34" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE34" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="12.75">
       <c r="A35" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>9</v>
@@ -4320,43 +4332,43 @@
         <v>13</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H35" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="58" t="s">
-        <v>32</v>
+      <c r="I35" s="57" t="s">
+        <v>33</v>
       </c>
       <c r="J35" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K35" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="58" t="s">
-        <v>32</v>
-      </c>
-      <c r="N35" s="58" t="s">
-        <v>32</v>
-      </c>
-      <c r="O35" s="58" t="s">
+      <c r="K35" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="M35" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="O35" s="57" t="s">
         <v>16</v>
       </c>
       <c r="P35" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q35" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q35" s="57" t="s">
         <v>17</v>
       </c>
       <c r="R35" s="35" t="s">
         <v>30</v>
       </c>
       <c r="S35" s="19" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="T35" s="19" t="s">
         <v>9</v>
@@ -4367,19 +4379,19 @@
       <c r="V35" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="W35" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="X35" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y35" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z35" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA35" s="58" t="s">
+      <c r="W35" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="X35" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y35" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z35" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA35" s="57" t="s">
         <v>17</v>
       </c>
       <c r="AB35" s="19" t="s">
@@ -4397,16 +4409,16 @@
     </row>
     <row r="36" spans="1:31" ht="12.75">
       <c r="A36" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>9</v>
@@ -4414,32 +4426,32 @@
       <c r="F36" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G36" s="58" t="s">
+      <c r="G36" s="57" t="s">
         <v>16</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="57" t="s">
         <v>17</v>
       </c>
       <c r="K36" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="L36" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="M36" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="N36" s="58" t="s">
+      <c r="L36" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="57" t="s">
         <v>17</v>
       </c>
       <c r="O36" s="31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P36" s="19" t="s">
         <v>18</v>
@@ -4448,22 +4460,22 @@
         <v>17</v>
       </c>
       <c r="R36" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S36" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="S36" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="T36" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="U36" s="49" t="s">
+      <c r="T36" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="U36" s="48" t="s">
         <v>46</v>
       </c>
       <c r="V36" s="35" t="s">
         <v>16</v>
       </c>
       <c r="W36" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X36" s="19" t="s">
         <v>18</v>
@@ -4481,18 +4493,18 @@
         <v>18</v>
       </c>
       <c r="AC36" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD36" s="34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AE36" s="34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="12.75">
       <c r="A37" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>16</v>
@@ -4519,64 +4531,64 @@
         <v>18</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="L37" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="L37" s="57" t="s">
         <v>16</v>
       </c>
       <c r="M37" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N37" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O37" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P37" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q37" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R37" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="S37" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="T37" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="U37" s="49" t="s">
+      <c r="S37" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="T37" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="U37" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="V37" s="49" t="s">
+      <c r="V37" s="48" t="s">
         <v>46</v>
       </c>
       <c r="W37" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X37" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y37" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z37" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA37" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB37" s="35" t="s">
         <v>16</v>
       </c>
       <c r="AC37" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD37" s="34" t="s">
         <v>38</v>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29303"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E04E8F35-ED9D-42C9-9198-FE8F93DAA43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{362A1499-E8AA-4D26-AD39-77A31DAD3191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="agosto" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">agosto!$A$1:$AE$37</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="88">
   <si>
     <t>Lunes</t>
   </si>
@@ -201,85 +204,88 @@
     <t>SARA SOFIA CASAS CHARCAS</t>
   </si>
   <si>
-    <t>16:00 - 21:00</t>
+    <t>12:00 - 20:00</t>
+  </si>
+  <si>
+    <t>KELLY KATHERINE LOPEZ CHINGUAL</t>
+  </si>
+  <si>
+    <t>GABRIELA ALEJANDRA QUIROGA ESPITIA</t>
+  </si>
+  <si>
+    <t>15:00 - 20:00</t>
+  </si>
+  <si>
+    <t>DANIEL LOAIZA JIMENEZ</t>
+  </si>
+  <si>
+    <t>CARLOS DANIEL PATIÑO ALVAREZ</t>
+  </si>
+  <si>
+    <t>PAOLA ANDREA BARRETO PATARROYO</t>
+  </si>
+  <si>
+    <t>calamidad familiar</t>
+  </si>
+  <si>
+    <t>JENNY ALEXANDRA ANTONIO ANTONIO</t>
+  </si>
+  <si>
+    <t>KEILA DEL CARMEN BENAVIDEZ OLIVERA</t>
+  </si>
+  <si>
+    <t>NICOLAS JOSE CABANZO SANTOS</t>
+  </si>
+  <si>
+    <t>BRIAM ERNESTO NIETO HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ANGIE CAROLINA NARANJO HERRERA</t>
+  </si>
+  <si>
+    <t>13:00 - 20:00</t>
+  </si>
+  <si>
+    <t>JHOSNMAN ARLEY RODRIGUEZ ARIAS</t>
+  </si>
+  <si>
+    <t>PAOLA STEFANIA ARIAS PEÑA</t>
+  </si>
+  <si>
+    <t>XIOMARA CATHERIN SALGADO CUERVO</t>
+  </si>
+  <si>
+    <t>6:00 - 11:00</t>
+  </si>
+  <si>
+    <t>JORGE ARTURO BERNAL MARIN</t>
+  </si>
+  <si>
+    <t>JUAN CAMILO ROSAS ALARCON</t>
+  </si>
+  <si>
+    <t>10:00 - 18:00</t>
+  </si>
+  <si>
+    <t>HERNAN RICARDO BUSTAMANTE HERMIDA</t>
+  </si>
+  <si>
+    <t>EDGAR ALEJANDRO HERRERA SARMIENTO</t>
+  </si>
+  <si>
+    <t>ANA MARIA CAUSIL GARCIA</t>
+  </si>
+  <si>
+    <t>16:00 - 20:00</t>
+  </si>
+  <si>
+    <t>HEIDY ZULIEN ULLOA GARCES</t>
+  </si>
+  <si>
+    <t>ANA MILENA SOLANO BRAVO</t>
   </si>
   <si>
     <t>9:00 - 14:00</t>
-  </si>
-  <si>
-    <t>KELLY KATHERINE LOPEZ CHINGUAL</t>
-  </si>
-  <si>
-    <t>GABRIELA ALEJANDRA QUIROGA ESPITIA</t>
-  </si>
-  <si>
-    <t>15:00 - 20:00</t>
-  </si>
-  <si>
-    <t>DANIEL LOAIZA JIMENEZ</t>
-  </si>
-  <si>
-    <t>CARLOS DANIEL PATIÑO ALVAREZ</t>
-  </si>
-  <si>
-    <t>PAOLA ANDREA BARRETO PATARROYO</t>
-  </si>
-  <si>
-    <t>JENNY ALEXANDRA ANTONIO ANTONIO</t>
-  </si>
-  <si>
-    <t>KEILA DEL CARMEN BENAVIDEZ OLIVERA</t>
-  </si>
-  <si>
-    <t>NICOLAS JOSE CABANZO SANTOS</t>
-  </si>
-  <si>
-    <t>BRIAM ERNESTO NIETO HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ANGIE CAROLINA NARANJO HERRERA</t>
-  </si>
-  <si>
-    <t>13:00 - 20:00</t>
-  </si>
-  <si>
-    <t>JHOSNMAN ARLEY RODRIGUEZ ARIAS</t>
-  </si>
-  <si>
-    <t>PAOLA STEFANIA ARIAS PEÑA</t>
-  </si>
-  <si>
-    <t>XIOMARA CATHERIN SALGADO CUERVO</t>
-  </si>
-  <si>
-    <t>6:00 - 11:00</t>
-  </si>
-  <si>
-    <t>JORGE ARTURO BERNAL MARIN</t>
-  </si>
-  <si>
-    <t>JUAN CAMILO ROSAS ALARCON</t>
-  </si>
-  <si>
-    <t>10:00 - 18:00</t>
-  </si>
-  <si>
-    <t>HERNAN RICARDO BUSTAMANTE HERMIDA</t>
-  </si>
-  <si>
-    <t>EDGAR ALEJANDRO HERRERA SARMIENTO</t>
-  </si>
-  <si>
-    <t>ANA MARIA CAUSIL GARCIA</t>
-  </si>
-  <si>
-    <t>16:00 - 20:00</t>
-  </si>
-  <si>
-    <t>HEIDY ZULIEN ULLOA GARCES</t>
-  </si>
-  <si>
-    <t>ANA MILENA SOLANO BRAVO</t>
   </si>
   <si>
     <t>OSWALDO FORERO PATIÑO</t>
@@ -670,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -842,9 +848,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
@@ -1068,21 +1071,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AE37"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="22.140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" customWidth="1"/>
-    <col min="4" max="5" width="22.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" customWidth="1"/>
-    <col min="8" max="8" width="25.85546875" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="25.85546875" customWidth="1"/>
-    <col min="11" max="11" width="27.85546875" customWidth="1"/>
-    <col min="12" max="12" width="26.5703125" customWidth="1"/>
-    <col min="13" max="13" width="27.7109375" customWidth="1"/>
-    <col min="14" max="31" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -2277,20 +2268,20 @@
       <c r="R13" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="S13" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="T13" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="U13" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="V13" s="35" t="s">
-        <v>40</v>
+      <c r="S13" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="T13" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="U13" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="V13" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="W13" s="35" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="X13" s="35" t="s">
         <v>52</v>
@@ -2372,20 +2363,20 @@
       <c r="R14" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="S14" s="35" t="s">
-        <v>16</v>
+      <c r="S14" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="T14" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="U14" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="V14" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="W14" s="31" t="s">
         <v>50</v>
-      </c>
-      <c r="U14" s="62" t="s">
-        <v>47</v>
-      </c>
-      <c r="V14" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="W14" s="46" t="s">
-        <v>33</v>
       </c>
       <c r="X14" s="46" t="s">
         <v>18</v>
@@ -2467,20 +2458,20 @@
       <c r="R15" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="S15" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="35" t="s">
+      <c r="S15" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="U15" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="V15" s="35" t="s">
+      <c r="T15" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="U15" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="V15" s="26" t="s">
         <v>16</v>
       </c>
       <c r="W15" s="35" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="X15" s="35" t="s">
         <v>30</v>
@@ -2509,7 +2500,7 @@
     </row>
     <row r="16" spans="1:31" ht="12.75">
       <c r="A16" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>17</v>
@@ -2562,20 +2553,20 @@
       <c r="R16" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="S16" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="T16" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="U16" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="V16" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="W16" s="34" t="s">
-        <v>10</v>
+      <c r="S16" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="U16" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="V16" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="W16" s="19" t="s">
+        <v>9</v>
       </c>
       <c r="X16" s="35" t="s">
         <v>16</v>
@@ -2604,10 +2595,10 @@
     </row>
     <row r="17" spans="1:31" ht="12.75">
       <c r="A17" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>59</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>60</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>18</v>
@@ -2657,10 +2648,10 @@
       <c r="R17" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="S17" s="63" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" s="63" t="s">
+      <c r="S17" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="T17" s="62" t="s">
         <v>18</v>
       </c>
       <c r="U17" s="44" t="s">
@@ -2699,7 +2690,7 @@
     </row>
     <row r="18" spans="1:31" ht="12.75">
       <c r="A18" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>47</v>
@@ -2794,7 +2785,7 @@
     </row>
     <row r="19" spans="1:31" ht="12.75">
       <c r="A19" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>38</v>
@@ -2889,7 +2880,7 @@
     </row>
     <row r="20" spans="1:31" ht="12.75">
       <c r="A20" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>18</v>
@@ -2940,25 +2931,25 @@
         <v>18</v>
       </c>
       <c r="R20" s="26" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="S20" s="26" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="T20" s="26" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="U20" s="26" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="V20" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="W20" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="X20" s="31" t="s">
-        <v>46</v>
+      <c r="W20" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="X20" s="26" t="s">
+        <v>63</v>
       </c>
       <c r="Y20" s="31" t="s">
         <v>46</v>
@@ -3133,10 +3124,10 @@
         <v>47</v>
       </c>
       <c r="S22" s="26" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T22" s="26" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="U22" s="26" t="s">
         <v>51</v>
@@ -3231,7 +3222,7 @@
         <v>18</v>
       </c>
       <c r="T23" s="26" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="U23" s="26" t="s">
         <v>33</v>
@@ -3893,13 +3884,13 @@
         <v>76</v>
       </c>
       <c r="S30" s="26" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="T30" s="26" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="U30" s="26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="V30" s="26" t="s">
         <v>16</v>
@@ -4332,7 +4323,7 @@
         <v>13</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="H35" s="19" t="s">
         <v>16</v>
@@ -4409,7 +4400,7 @@
     </row>
     <row r="36" spans="1:31" ht="12.75">
       <c r="A36" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" s="38" t="s">
         <v>33</v>
@@ -4496,15 +4487,15 @@
         <v>26</v>
       </c>
       <c r="AD36" s="34" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="AE36" s="34" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="12.75">
       <c r="A37" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>16</v>
@@ -4531,10 +4522,10 @@
         <v>18</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L37" s="57" t="s">
         <v>16</v>
@@ -4570,10 +4561,10 @@
         <v>46</v>
       </c>
       <c r="W37" s="19" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="X37" s="19" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Y37" s="19" t="s">
         <v>33</v>
@@ -4598,6 +4589,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AE37" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
 </file>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{362A1499-E8AA-4D26-AD39-77A31DAD3191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92114415-749B-4116-9B6F-4BFA0AD95F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="91">
   <si>
     <t>Lunes</t>
   </si>
@@ -138,15 +138,15 @@
     <t>14:00 - 21:00</t>
   </si>
   <si>
+    <t>9:00 - 15:00</t>
+  </si>
+  <si>
     <t>17:00 - 22:00</t>
   </si>
   <si>
     <t>13:00 - 22:00</t>
   </si>
   <si>
-    <t>9:00 - 15:00</t>
-  </si>
-  <si>
     <t>FABER SEBASTIAN FÚQUENE HERNANDEZ</t>
   </si>
   <si>
@@ -171,6 +171,9 @@
     <t>14:00 - 20:00</t>
   </si>
   <si>
+    <t>8:00 - 15:00</t>
+  </si>
+  <si>
     <t>LOREN YIRETH INDABURO VARGAS</t>
   </si>
   <si>
@@ -186,9 +189,6 @@
     <t>JUAN DAVID ORJUELA MORALES</t>
   </si>
   <si>
-    <t>8:00 - 15:00</t>
-  </si>
-  <si>
     <t>7:00 - 13:00</t>
   </si>
   <si>
@@ -207,6 +207,12 @@
     <t>12:00 - 20:00</t>
   </si>
   <si>
+    <t>16:00 - 21:00</t>
+  </si>
+  <si>
+    <t>9:00 - 14:00</t>
+  </si>
+  <si>
     <t>KELLY KATHERINE LOPEZ CHINGUAL</t>
   </si>
   <si>
@@ -228,6 +234,9 @@
     <t>calamidad familiar</t>
   </si>
   <si>
+    <t xml:space="preserve">Calamidad Familiar </t>
+  </si>
+  <si>
     <t>JENNY ALEXANDRA ANTONIO ANTONIO</t>
   </si>
   <si>
@@ -285,9 +294,6 @@
     <t>ANA MILENA SOLANO BRAVO</t>
   </si>
   <si>
-    <t>9:00 - 14:00</t>
-  </si>
-  <si>
     <t>OSWALDO FORERO PATIÑO</t>
   </si>
   <si>
@@ -298,6 +304,9 @@
   </si>
   <si>
     <t>13:00 - 19:00</t>
+  </si>
+  <si>
+    <t>12:00 - 18:00</t>
   </si>
 </sst>
 </file>
@@ -676,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -851,6 +860,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1535,8 +1547,8 @@
       <c r="AA5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AB5" s="25" t="s">
-        <v>18</v>
+      <c r="AB5" s="60" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="60" t="s">
         <v>13</v>
@@ -1720,10 +1732,10 @@
         <v>25</v>
       </c>
       <c r="Z7" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA7" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="61" t="s">
         <v>18</v>
@@ -1797,40 +1809,40 @@
         <v>30</v>
       </c>
       <c r="T8" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="U8" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="U8" s="43" t="s">
         <v>30</v>
       </c>
       <c r="V8" s="35" t="s">
         <v>16</v>
       </c>
       <c r="W8" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="X8" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y8" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA8" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB8" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC8" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD8" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="X8" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y8" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z8" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA8" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB8" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD8" s="34" t="s">
-        <v>36</v>
-      </c>
       <c r="AE8" s="34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="12.75">
@@ -2087,8 +2099,8 @@
       <c r="U11" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="V11" s="35" t="s">
-        <v>33</v>
+      <c r="V11" s="34" t="s">
+        <v>45</v>
       </c>
       <c r="W11" s="34" t="s">
         <v>30</v>
@@ -2120,25 +2132,25 @@
     </row>
     <row r="12" spans="1:31" ht="12.75">
       <c r="A12" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H12" s="26" t="s">
         <v>16</v>
@@ -2150,7 +2162,7 @@
         <v>17</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L12" s="33" t="s">
         <v>40</v>
@@ -2171,7 +2183,7 @@
         <v>9</v>
       </c>
       <c r="R12" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S12" s="26" t="s">
         <v>13</v>
@@ -2209,19 +2221,19 @@
       <c r="AD12" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="AE12" s="19" t="s">
+      <c r="AE12" s="42" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="12.75">
       <c r="A13" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>9</v>
@@ -2230,16 +2242,16 @@
         <v>30</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G13" s="42" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H13" s="31" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J13" s="32" t="s">
         <v>9</v>
@@ -2263,25 +2275,25 @@
         <v>9</v>
       </c>
       <c r="Q13" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R13" s="31" t="s">
         <v>16</v>
       </c>
       <c r="S13" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="T13" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="U13" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="V13" s="26" t="s">
-        <v>16</v>
+        <v>45</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="U13" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="V13" s="35" t="s">
+        <v>40</v>
       </c>
       <c r="W13" s="35" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="X13" s="35" t="s">
         <v>52</v>
@@ -2313,19 +2325,19 @@
         <v>53</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>54</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>10</v>
@@ -2355,37 +2367,37 @@
         <v>26</v>
       </c>
       <c r="P14" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q14" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R14" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="S14" s="26" t="s">
         <v>18</v>
       </c>
       <c r="T14" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="U14" s="26" t="s">
-        <v>33</v>
+        <v>45</v>
+      </c>
+      <c r="U14" s="63" t="s">
+        <v>48</v>
       </c>
       <c r="V14" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="W14" s="31" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="W14" s="46" t="s">
+        <v>33</v>
       </c>
       <c r="X14" s="46" t="s">
         <v>18</v>
       </c>
       <c r="Y14" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z14" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA14" s="47" t="s">
         <v>38</v>
@@ -2408,16 +2420,16 @@
         <v>55</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>52</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F15" s="26" t="s">
         <v>12</v>
@@ -2429,7 +2441,7 @@
         <v>16</v>
       </c>
       <c r="I15" s="31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J15" s="31" t="s">
         <v>26</v>
@@ -2461,17 +2473,17 @@
       <c r="S15" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="T15" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="U15" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="V15" s="26" t="s">
+      <c r="T15" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="U15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="35" t="s">
         <v>16</v>
       </c>
       <c r="W15" s="35" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="X15" s="35" t="s">
         <v>30</v>
@@ -2500,7 +2512,7 @@
     </row>
     <row r="16" spans="1:31" ht="12.75">
       <c r="A16" s="17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>17</v>
@@ -2527,7 +2539,7 @@
         <v>9</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K16" s="32" t="s">
         <v>38</v>
@@ -2556,17 +2568,17 @@
       <c r="S16" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="T16" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="U16" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="V16" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="W16" s="19" t="s">
-        <v>9</v>
+      <c r="T16" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="U16" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="V16" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="W16" s="34" t="s">
+        <v>10</v>
       </c>
       <c r="X16" s="35" t="s">
         <v>16</v>
@@ -2584,7 +2596,7 @@
         <v>30</v>
       </c>
       <c r="AC16" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AD16" s="34" t="s">
         <v>18</v>
@@ -2595,10 +2607,10 @@
     </row>
     <row r="17" spans="1:31" ht="12.75">
       <c r="A17" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>18</v>
@@ -2619,19 +2631,19 @@
         <v>10</v>
       </c>
       <c r="I17" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="26" t="s">
+      <c r="M17" s="26" t="s">
         <v>47</v>
-      </c>
-      <c r="K17" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="L17" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M17" s="26" t="s">
-        <v>46</v>
       </c>
       <c r="N17" s="26" t="s">
         <v>51</v>
@@ -2664,7 +2676,7 @@
         <v>16</v>
       </c>
       <c r="X17" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y17" s="46" t="s">
         <v>38</v>
@@ -2675,28 +2687,28 @@
       <c r="AA17" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="AB17" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC17" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD17" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE17" s="34" t="s">
+      <c r="AB17" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC17" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD17" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE17" s="43" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="12.75">
       <c r="A18" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>17</v>
@@ -2785,7 +2797,7 @@
     </row>
     <row r="19" spans="1:31" ht="12.75">
       <c r="A19" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>38</v>
@@ -2797,7 +2809,7 @@
         <v>30</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>18</v>
@@ -2815,22 +2827,22 @@
         <v>12</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L19" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M19" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N19" s="31" t="s">
         <v>10</v>
       </c>
       <c r="O19" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P19" s="43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q19" s="43" t="s">
         <v>25</v>
@@ -2880,7 +2892,7 @@
     </row>
     <row r="20" spans="1:31" ht="12.75">
       <c r="A20" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>18</v>
@@ -2904,22 +2916,22 @@
         <v>16</v>
       </c>
       <c r="I20" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="37" t="s">
+      <c r="M20" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="M20" s="31" t="s">
-        <v>46</v>
-      </c>
       <c r="N20" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O20" s="31" t="s">
         <v>16</v>
@@ -2931,37 +2943,37 @@
         <v>18</v>
       </c>
       <c r="R20" s="26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="S20" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="T20" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="U20" s="26" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="T20" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="U20" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="V20" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="W20" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="X20" s="26" t="s">
-        <v>63</v>
+      <c r="W20" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="X20" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="Y20" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z20" s="31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA20" s="31" t="s">
         <v>38</v>
       </c>
       <c r="AB20" s="35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AC20" s="34" t="s">
         <v>16</v>
@@ -2975,7 +2987,7 @@
     </row>
     <row r="21" spans="1:31" ht="12.75">
       <c r="A21" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>15</v>
@@ -3040,22 +3052,22 @@
       <c r="V21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="W21" s="31" t="s">
+      <c r="W21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="X21" s="31" t="s">
+      <c r="X21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="Y21" s="31" t="s">
+      <c r="Y21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="Z21" s="31" t="s">
+      <c r="Z21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="AA21" s="31" t="s">
+      <c r="AA21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="AB21" s="31" t="s">
+      <c r="AB21" s="37" t="s">
         <v>15</v>
       </c>
       <c r="AC21" s="34" t="s">
@@ -3064,22 +3076,22 @@
       <c r="AD21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="AE21" s="19" t="s">
+      <c r="AE21" s="42" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="12.75">
       <c r="A22" s="17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>18</v>
@@ -3097,7 +3109,7 @@
         <v>40</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K22" s="35" t="s">
         <v>40</v>
@@ -3115,16 +3127,16 @@
         <v>16</v>
       </c>
       <c r="P22" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q22" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R22" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S22" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T22" s="26" t="s">
         <v>30</v>
@@ -3160,12 +3172,12 @@
         <v>38</v>
       </c>
       <c r="AE22" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="12.75">
       <c r="A23" s="17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>17</v>
@@ -3231,19 +3243,19 @@
         <v>16</v>
       </c>
       <c r="W23" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="X23" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y23" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z23" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA23" s="31" t="s">
         <v>47</v>
-      </c>
-      <c r="Y23" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z23" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA23" s="31" t="s">
-        <v>46</v>
       </c>
       <c r="AB23" s="31" t="s">
         <v>38</v>
@@ -3260,7 +3272,7 @@
     </row>
     <row r="24" spans="1:31" ht="12.75">
       <c r="A24" s="17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>17</v>
@@ -3302,13 +3314,13 @@
         <v>9</v>
       </c>
       <c r="O24" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P24" s="34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Q24" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R24" s="35" t="s">
         <v>18</v>
@@ -3355,7 +3367,7 @@
     </row>
     <row r="25" spans="1:31" ht="12.75">
       <c r="A25" s="17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>26</v>
@@ -3364,7 +3376,7 @@
         <v>26</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>26</v>
@@ -3450,7 +3462,7 @@
     </row>
     <row r="26" spans="1:31" ht="12.75">
       <c r="A26" s="17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>17</v>
@@ -3507,10 +3519,10 @@
         <v>12</v>
       </c>
       <c r="T26" s="35" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="U26" s="35" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="V26" s="40" t="s">
         <v>16</v>
@@ -3528,7 +3540,7 @@
         <v>17</v>
       </c>
       <c r="AA26" s="34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB26" s="34" t="s">
         <v>26</v>
@@ -3545,7 +3557,7 @@
     </row>
     <row r="27" spans="1:31" ht="12.75">
       <c r="A27" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B27" s="41" t="s">
         <v>26</v>
@@ -3554,13 +3566,13 @@
         <v>26</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="31" t="s">
         <v>16</v>
@@ -3599,7 +3611,7 @@
         <v>30</v>
       </c>
       <c r="S27" s="34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="T27" s="35" t="s">
         <v>16</v>
@@ -3607,43 +3619,43 @@
       <c r="U27" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="V27" s="34" t="s">
-        <v>50</v>
+      <c r="V27" s="35" t="s">
+        <v>33</v>
       </c>
       <c r="W27" s="34" t="s">
         <v>26</v>
       </c>
       <c r="X27" s="34" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="Y27" s="34" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="Z27" s="34" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA27" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB27" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC27" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB27" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC27" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AD27" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE27" s="26" t="s">
+      <c r="AD27" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE27" s="41" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="12.75">
       <c r="A28" s="17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>12</v>
@@ -3667,7 +3679,7 @@
         <v>18</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K28" s="37" t="s">
         <v>9</v>
@@ -3712,16 +3724,16 @@
         <v>24</v>
       </c>
       <c r="Y28" s="34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z28" s="34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA28" s="34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AB28" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AC28" s="34" t="s">
         <v>33</v>
@@ -3735,7 +3747,7 @@
     </row>
     <row r="29" spans="1:31" ht="12.75">
       <c r="A29" s="17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>18</v>
@@ -3759,7 +3771,7 @@
         <v>33</v>
       </c>
       <c r="I29" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J29" s="31" t="s">
         <v>30</v>
@@ -3830,16 +3842,16 @@
     </row>
     <row r="30" spans="1:31" ht="12.75">
       <c r="A30" s="17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>38</v>
@@ -3854,34 +3866,34 @@
         <v>16</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L30" s="56" t="s">
         <v>16</v>
       </c>
       <c r="M30" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O30" s="52" t="s">
         <v>9</v>
       </c>
       <c r="P30" s="26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q30" s="26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="R30" s="26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S30" s="26" t="s">
         <v>56</v>
@@ -3911,13 +3923,13 @@
         <v>18</v>
       </c>
       <c r="AB30" s="35" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AC30" s="26" t="s">
         <v>24</v>
       </c>
       <c r="AD30" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE30" s="26" t="s">
         <v>38</v>
@@ -3925,7 +3937,7 @@
     </row>
     <row r="31" spans="1:31" ht="12.75">
       <c r="A31" s="17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B31" s="42" t="s">
         <v>9</v>
@@ -3949,7 +3961,7 @@
         <v>16</v>
       </c>
       <c r="I31" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J31" s="35" t="s">
         <v>18</v>
@@ -3961,7 +3973,7 @@
         <v>30</v>
       </c>
       <c r="M31" s="31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N31" s="31" t="s">
         <v>10</v>
@@ -3982,7 +3994,7 @@
         <v>17</v>
       </c>
       <c r="T31" s="39" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="U31" s="39" t="s">
         <v>18</v>
@@ -4009,7 +4021,7 @@
         <v>9</v>
       </c>
       <c r="AC31" s="58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD31" s="35" t="s">
         <v>18</v>
@@ -4020,7 +4032,7 @@
     </row>
     <row r="32" spans="1:31" ht="12.75">
       <c r="A32" s="17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>25</v>
@@ -4110,12 +4122,12 @@
         <v>16</v>
       </c>
       <c r="AE32" s="34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="12.75">
       <c r="A33" s="17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>17</v>
@@ -4148,16 +4160,16 @@
         <v>31</v>
       </c>
       <c r="L33" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M33" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N33" s="48" t="s">
         <v>16</v>
       </c>
       <c r="O33" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P33" s="34" t="s">
         <v>12</v>
@@ -4187,16 +4199,16 @@
         <v>9</v>
       </c>
       <c r="Y33" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z33" s="34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AA33" s="48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AB33" s="48" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AC33" s="34" t="s">
         <v>16</v>
@@ -4210,7 +4222,7 @@
     </row>
     <row r="34" spans="1:31" ht="12.75">
       <c r="A34" s="17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>22</v>
@@ -4237,13 +4249,13 @@
         <v>9</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" s="19" t="s">
         <v>9</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M34" s="19" t="s">
         <v>9</v>
@@ -4305,13 +4317,13 @@
     </row>
     <row r="35" spans="1:31" ht="12.75">
       <c r="A35" s="17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D35" s="26" t="s">
         <v>52</v>
@@ -4323,7 +4335,7 @@
         <v>13</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="H35" s="19" t="s">
         <v>16</v>
@@ -4359,7 +4371,7 @@
         <v>30</v>
       </c>
       <c r="S35" s="19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T35" s="19" t="s">
         <v>9</v>
@@ -4400,7 +4412,7 @@
     </row>
     <row r="36" spans="1:31" ht="12.75">
       <c r="A36" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B36" s="38" t="s">
         <v>33</v>
@@ -4460,7 +4472,7 @@
         <v>9</v>
       </c>
       <c r="U36" s="48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V36" s="35" t="s">
         <v>16</v>
@@ -4487,15 +4499,15 @@
         <v>26</v>
       </c>
       <c r="AD36" s="34" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="AE36" s="34" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="12.75">
       <c r="A37" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>16</v>
@@ -4522,10 +4534,10 @@
         <v>18</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L37" s="57" t="s">
         <v>16</v>
@@ -4558,13 +4570,13 @@
         <v>13</v>
       </c>
       <c r="V37" s="48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W37" s="19" t="s">
         <v>9</v>
       </c>
       <c r="X37" s="19" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="Y37" s="19" t="s">
         <v>33</v>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92114415-749B-4116-9B6F-4BFA0AD95F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F484FE77-28AD-4EB5-944D-0E121019201F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -204,76 +204,76 @@
     <t>SARA SOFIA CASAS CHARCAS</t>
   </si>
   <si>
+    <t>16:00 - 21:00</t>
+  </si>
+  <si>
+    <t>9:00 - 14:00</t>
+  </si>
+  <si>
+    <t>KELLY KATHERINE LOPEZ CHINGUAL</t>
+  </si>
+  <si>
+    <t>GABRIELA ALEJANDRA QUIROGA ESPITIA</t>
+  </si>
+  <si>
+    <t>15:00 - 20:00</t>
+  </si>
+  <si>
+    <t>DANIEL LOAIZA JIMENEZ</t>
+  </si>
+  <si>
+    <t>CARLOS DANIEL PATIÑO ALVAREZ</t>
+  </si>
+  <si>
+    <t>PAOLA ANDREA BARRETO PATARROYO</t>
+  </si>
+  <si>
+    <t>calamidad familiar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calamidad Familiar </t>
+  </si>
+  <si>
+    <t>JENNY ALEXANDRA ANTONIO ANTONIO</t>
+  </si>
+  <si>
+    <t>KEILA DEL CARMEN BENAVIDEZ OLIVERA</t>
+  </si>
+  <si>
+    <t>NICOLAS JOSE CABANZO SANTOS</t>
+  </si>
+  <si>
+    <t>BRIAM ERNESTO NIETO HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ANGIE CAROLINA NARANJO HERRERA</t>
+  </si>
+  <si>
+    <t>13:00 - 20:00</t>
+  </si>
+  <si>
+    <t>JHOSNMAN ARLEY RODRIGUEZ ARIAS</t>
+  </si>
+  <si>
+    <t>PAOLA STEFANIA ARIAS PEÑA</t>
+  </si>
+  <si>
+    <t>XIOMARA CATHERIN SALGADO CUERVO</t>
+  </si>
+  <si>
+    <t>6:00 - 11:00</t>
+  </si>
+  <si>
+    <t>JORGE ARTURO BERNAL MARIN</t>
+  </si>
+  <si>
+    <t>JUAN CAMILO ROSAS ALARCON</t>
+  </si>
+  <si>
+    <t>10:00 - 18:00</t>
+  </si>
+  <si>
     <t>12:00 - 20:00</t>
-  </si>
-  <si>
-    <t>16:00 - 21:00</t>
-  </si>
-  <si>
-    <t>9:00 - 14:00</t>
-  </si>
-  <si>
-    <t>KELLY KATHERINE LOPEZ CHINGUAL</t>
-  </si>
-  <si>
-    <t>GABRIELA ALEJANDRA QUIROGA ESPITIA</t>
-  </si>
-  <si>
-    <t>15:00 - 20:00</t>
-  </si>
-  <si>
-    <t>DANIEL LOAIZA JIMENEZ</t>
-  </si>
-  <si>
-    <t>CARLOS DANIEL PATIÑO ALVAREZ</t>
-  </si>
-  <si>
-    <t>PAOLA ANDREA BARRETO PATARROYO</t>
-  </si>
-  <si>
-    <t>calamidad familiar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calamidad Familiar </t>
-  </si>
-  <si>
-    <t>JENNY ALEXANDRA ANTONIO ANTONIO</t>
-  </si>
-  <si>
-    <t>KEILA DEL CARMEN BENAVIDEZ OLIVERA</t>
-  </si>
-  <si>
-    <t>NICOLAS JOSE CABANZO SANTOS</t>
-  </si>
-  <si>
-    <t>BRIAM ERNESTO NIETO HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ANGIE CAROLINA NARANJO HERRERA</t>
-  </si>
-  <si>
-    <t>13:00 - 20:00</t>
-  </si>
-  <si>
-    <t>JHOSNMAN ARLEY RODRIGUEZ ARIAS</t>
-  </si>
-  <si>
-    <t>PAOLA STEFANIA ARIAS PEÑA</t>
-  </si>
-  <si>
-    <t>XIOMARA CATHERIN SALGADO CUERVO</t>
-  </si>
-  <si>
-    <t>6:00 - 11:00</t>
-  </si>
-  <si>
-    <t>JORGE ARTURO BERNAL MARIN</t>
-  </si>
-  <si>
-    <t>JUAN CAMILO ROSAS ALARCON</t>
-  </si>
-  <si>
-    <t>10:00 - 18:00</t>
   </si>
   <si>
     <t>HERNAN RICARDO BUSTAMANTE HERMIDA</t>
@@ -2281,7 +2281,7 @@
         <v>16</v>
       </c>
       <c r="S13" s="26" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="T13" s="34" t="s">
         <v>9</v>
@@ -2376,7 +2376,7 @@
         <v>45</v>
       </c>
       <c r="S14" s="26" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T14" s="26" t="s">
         <v>45</v>
@@ -2471,19 +2471,19 @@
         <v>18</v>
       </c>
       <c r="S15" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="T15" s="35" t="s">
+      <c r="U15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="W15" s="35" t="s">
         <v>57</v>
-      </c>
-      <c r="U15" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="V15" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="W15" s="35" t="s">
-        <v>58</v>
       </c>
       <c r="X15" s="35" t="s">
         <v>30</v>
@@ -2512,7 +2512,7 @@
     </row>
     <row r="16" spans="1:31" ht="12.75">
       <c r="A16" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>17</v>
@@ -2566,7 +2566,7 @@
         <v>30</v>
       </c>
       <c r="S16" s="48" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T16" s="35" t="s">
         <v>17</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="17" spans="1:31" ht="12.75">
       <c r="A17" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>60</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>61</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>18</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="18" spans="1:31" ht="12.75">
       <c r="A18" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>48</v>
@@ -2797,7 +2797,7 @@
     </row>
     <row r="19" spans="1:31" ht="12.75">
       <c r="A19" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>38</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="20" spans="1:31" ht="12.75">
       <c r="A20" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>18</v>
@@ -2943,25 +2943,25 @@
         <v>18</v>
       </c>
       <c r="R20" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S20" s="26" t="s">
         <v>65</v>
       </c>
       <c r="T20" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U20" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V20" s="26" t="s">
         <v>16</v>
       </c>
       <c r="W20" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X20" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y20" s="31" t="s">
         <v>47</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="21" spans="1:31" ht="12.75">
       <c r="A21" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>15</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="22" spans="1:31" ht="12.75">
       <c r="A22" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>45</v>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="23" spans="1:31" ht="12.75">
       <c r="A23" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>17</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="24" spans="1:31" ht="12.75">
       <c r="A24" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="31" t="s">
         <v>17</v>
@@ -3367,16 +3367,16 @@
     </row>
     <row r="25" spans="1:31" ht="12.75">
       <c r="A25" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>72</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>26</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="26" spans="1:31" ht="12.75">
       <c r="A26" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>17</v>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="27" spans="1:31" ht="12.75">
       <c r="A27" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="41" t="s">
         <v>26</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="28" spans="1:31" ht="12.75">
       <c r="A28" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>34</v>
@@ -3679,7 +3679,7 @@
         <v>18</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K28" s="37" t="s">
         <v>9</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="29" spans="1:31" ht="12.75">
       <c r="A29" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>18</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="30" spans="1:31" ht="12.75">
       <c r="A30" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>45</v>
@@ -3887,19 +3887,19 @@
         <v>9</v>
       </c>
       <c r="P30" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="R30" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="S30" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="Q30" s="26" t="s">
+      <c r="T30" s="26" t="s">
         <v>79</v>
-      </c>
-      <c r="R30" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="S30" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="T30" s="26" t="s">
-        <v>56</v>
       </c>
       <c r="U30" s="26" t="s">
         <v>41</v>
@@ -4181,7 +4181,7 @@
         <v>38</v>
       </c>
       <c r="S33" s="19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T33" s="19" t="s">
         <v>18</v>
@@ -4335,7 +4335,7 @@
         <v>13</v>
       </c>
       <c r="G35" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H35" s="19" t="s">
         <v>16</v>
@@ -4499,10 +4499,10 @@
         <v>26</v>
       </c>
       <c r="AD36" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AE36" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="12.75">

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29406"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FD7C18D-0E84-4E1F-AB91-F33975E0AB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16D42461-65D6-4624-8326-5033D46AD05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,27 +150,27 @@
     <t>FABER SEBASTIAN FÚQUENE HERNANDEZ</t>
   </si>
   <si>
+    <t>7:00 - 14:00</t>
+  </si>
+  <si>
+    <t>FREDY ALEXANDER CALCETERO PARDO</t>
+  </si>
+  <si>
+    <t>8:00 - 17:00</t>
+  </si>
+  <si>
+    <t>16:00 - 21:00</t>
+  </si>
+  <si>
+    <t>8:00 - 15:00</t>
+  </si>
+  <si>
+    <t>8:00 - 14:00</t>
+  </si>
+  <si>
     <t>16:00 - 22:00</t>
   </si>
   <si>
-    <t>7:00 - 14:00</t>
-  </si>
-  <si>
-    <t>FREDY ALEXANDER CALCETERO PARDO</t>
-  </si>
-  <si>
-    <t>8:00 - 17:00</t>
-  </si>
-  <si>
-    <t>16:00 - 21:00</t>
-  </si>
-  <si>
-    <t>8:00 - 15:00</t>
-  </si>
-  <si>
-    <t>8:00 - 14:00</t>
-  </si>
-  <si>
     <t>JULIAN DAVID CHAPARRO VARGAS</t>
   </si>
   <si>
@@ -183,13 +183,13 @@
     <t>7:00 - 15:00</t>
   </si>
   <si>
+    <t>15:00 - 21:00</t>
+  </si>
+  <si>
     <t>JUAN DAVID ORJUELA MORALES</t>
   </si>
   <si>
     <t>09:00 - 15:00</t>
-  </si>
-  <si>
-    <t>15:00 - 21:00</t>
   </si>
   <si>
     <t>DAYANA ANDREA RAMIREZ BERNAL</t>
@@ -652,9 +652,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -666,13 +663,9 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -683,6 +676,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1097,7 +1097,7 @@
       </c>
     </row>
     <row r="3" spans="1:32" ht="12.75">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1195,7 +1195,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="12.75">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -1264,8 +1264,8 @@
       <c r="W4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="X4" s="8" t="s">
-        <v>17</v>
+      <c r="X4" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="Y4" s="11" t="s">
         <v>14</v>
@@ -1293,7 +1293,7 @@
       </c>
     </row>
     <row r="5" spans="1:32" ht="12.75">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -1391,7 +1391,7 @@
       </c>
     </row>
     <row r="6" spans="1:32" ht="12.75">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1469,7 +1469,7 @@
       <c r="Z6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AA6" s="31" t="s">
+      <c r="AA6" s="30" t="s">
         <v>25</v>
       </c>
       <c r="AB6" s="8" t="s">
@@ -1489,7 +1489,7 @@
       </c>
     </row>
     <row r="7" spans="1:32" ht="12.75">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="18" t="s">
@@ -1587,25 +1587,25 @@
       </c>
     </row>
     <row r="8" spans="1:32" ht="12.75">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="32" t="s">
+      <c r="B8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="34" t="s">
+      <c r="F8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="31" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="20" t="s">
@@ -1629,13 +1629,13 @@
       <c r="N8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="32" t="s">
+      <c r="O8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="P8" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q8" s="32" t="s">
+      <c r="P8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="36" t="s">
         <v>14</v>
       </c>
       <c r="R8" s="21" t="s">
@@ -1665,7 +1665,7 @@
       <c r="Z8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AA8" s="32" t="s">
+      <c r="AA8" s="36" t="s">
         <v>14</v>
       </c>
       <c r="AB8" s="12" t="s">
@@ -1685,13 +1685,13 @@
       </c>
     </row>
     <row r="9" spans="1:32" ht="12.75">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="20" t="s">
@@ -1703,7 +1703,7 @@
       <c r="F9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="31" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="12" t="s">
@@ -1713,13 +1713,13 @@
         <v>18</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M9" s="20" t="s">
         <v>11</v>
@@ -1727,17 +1727,17 @@
       <c r="N9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="32" t="s">
+      <c r="O9" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="R9" s="32" t="s">
-        <v>39</v>
+      <c r="P9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="R9" s="36" t="s">
+        <v>38</v>
       </c>
       <c r="S9" s="12" t="s">
         <v>14</v>
@@ -1766,43 +1766,43 @@
       <c r="AA9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="AB9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF9" s="32" t="s">
+      <c r="AB9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF9" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="12.75">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="31" t="s">
         <v>41</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>42</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>17</v>
@@ -1825,20 +1825,20 @@
       <c r="N10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="32" t="s">
+      <c r="O10" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="P10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="P10" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q10" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="32" t="s">
-        <v>44</v>
-      </c>
       <c r="S10" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T10" s="20" t="s">
         <v>11</v>
@@ -1853,10 +1853,10 @@
         <v>25</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z10" s="12" t="s">
         <v>34</v>
@@ -1864,42 +1864,42 @@
       <c r="AA10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="AB10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF10" s="32" t="s">
+      <c r="AB10" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC10" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD10" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE10" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF10" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="12.75">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>45</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="36" t="s">
         <v>32</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="31" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="12" t="s">
@@ -1923,16 +1923,16 @@
       <c r="N11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="32" t="s">
+      <c r="O11" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q11" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="R11" s="32" t="s">
+      <c r="P11" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" s="36" t="s">
         <v>32</v>
       </c>
       <c r="S11" s="7" t="s">
@@ -1979,13 +1979,13 @@
       </c>
     </row>
     <row r="12" spans="1:32" ht="12.75">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="26" t="s">
         <v>47</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="37" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="23" t="s">
@@ -1997,7 +1997,7 @@
       <c r="F12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="24" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -2007,10 +2007,10 @@
         <v>12</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="L12" s="12" t="s">
         <v>34</v>
@@ -2021,32 +2021,32 @@
       <c r="N12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="P12" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q12" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="R12" s="32" t="s">
+      <c r="O12" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="R12" s="36" t="s">
         <v>17</v>
       </c>
       <c r="S12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="T12" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="U12" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="T12" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="U12" s="32" t="s">
-        <v>39</v>
-      </c>
       <c r="V12" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X12" s="12" t="s">
         <v>48</v>
@@ -2077,40 +2077,40 @@
       </c>
     </row>
     <row r="13" spans="1:32" ht="12.75">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>51</v>
-      </c>
       <c r="F13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="34" t="s">
+      <c r="G13" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="34" t="s">
+      <c r="K13" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="34" t="s">
+      <c r="L13" s="31" t="s">
         <v>14</v>
       </c>
       <c r="M13" s="20" t="s">
@@ -2119,16 +2119,16 @@
       <c r="N13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="O13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="P13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="R13" s="32" t="s">
+      <c r="O13" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="P13" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q13" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="R13" s="36" t="s">
         <v>33</v>
       </c>
       <c r="S13" s="12" t="s">
@@ -2144,19 +2144,19 @@
         <v>18</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y13" s="32" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="Y13" s="36" t="s">
+        <v>51</v>
       </c>
       <c r="Z13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="AA13" s="32" t="s">
-        <v>50</v>
+      <c r="AA13" s="36" t="s">
+        <v>51</v>
       </c>
       <c r="AB13" s="12" t="s">
         <v>48</v>
@@ -2175,13 +2175,13 @@
       </c>
     </row>
     <row r="14" spans="1:32" ht="12.75">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="26" t="s">
         <v>52</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="37" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="12" t="s">
@@ -2193,19 +2193,19 @@
       <c r="F14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="34" t="s">
+      <c r="G14" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="31" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="12" t="s">
@@ -2217,19 +2217,19 @@
       <c r="N14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O14" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" s="32" t="s">
+      <c r="O14" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="36" t="s">
         <v>21</v>
       </c>
       <c r="R14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="S14" s="24" t="s">
+      <c r="S14" s="20" t="s">
         <v>11</v>
       </c>
       <c r="T14" s="12" t="s">
@@ -2238,14 +2238,14 @@
       <c r="U14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="V14" s="20" t="s">
-        <v>11</v>
+      <c r="V14" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="W14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="X14" s="12" t="s">
-        <v>21</v>
+      <c r="X14" s="20" t="s">
+        <v>11</v>
       </c>
       <c r="Y14" s="12" t="s">
         <v>21</v>
@@ -2259,7 +2259,7 @@
       <c r="AB14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AC14" s="13" t="s">
+      <c r="AC14" s="12" t="s">
         <v>21</v>
       </c>
       <c r="AD14" s="12" t="s">
@@ -2273,38 +2273,38 @@
       </c>
     </row>
     <row r="15" spans="1:32" ht="12.75">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="39" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="34" t="s">
+      <c r="G15" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="34" t="s">
-        <v>39</v>
+      <c r="I15" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>38</v>
       </c>
       <c r="L15" s="12" t="s">
         <v>14</v>
@@ -2315,13 +2315,13 @@
       <c r="N15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="O15" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="P15" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q15" s="32" t="s">
+      <c r="O15" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q15" s="36" t="s">
         <v>17</v>
       </c>
       <c r="R15" s="12" t="s">
@@ -2371,13 +2371,13 @@
       </c>
     </row>
     <row r="16" spans="1:32" ht="12.75">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="26" t="s">
         <v>55</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="37" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="12" t="s">
@@ -2389,22 +2389,22 @@
       <c r="F16" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="34" t="s">
+      <c r="G16" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="K16" s="34" t="s">
+      <c r="K16" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="25" t="s">
+      <c r="L16" s="24" t="s">
         <v>19</v>
       </c>
       <c r="M16" s="20" t="s">
@@ -2413,14 +2413,14 @@
       <c r="N16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O16" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="P16" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q16" s="32" t="s">
-        <v>38</v>
+      <c r="O16" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="36" t="s">
+        <v>44</v>
       </c>
       <c r="R16" s="7" t="s">
         <v>36</v>
@@ -2441,19 +2441,19 @@
         <v>11</v>
       </c>
       <c r="X16" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y16" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z16" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA16" s="12" t="s">
         <v>36</v>
       </c>
       <c r="AB16" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AC16" s="12" t="s">
         <v>34</v>
@@ -2462,23 +2462,23 @@
         <v>34</v>
       </c>
       <c r="AE16" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AF16" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:32" ht="12.75">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="32" t="s">
+      <c r="C17" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="36" t="s">
         <v>36</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -2487,37 +2487,37 @@
       <c r="F17" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="J17" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="34" t="s">
+      <c r="G17" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="31" t="s">
         <v>34</v>
       </c>
       <c r="M17" s="20" t="s">
         <v>11</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="O17" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="O17" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="P17" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q17" s="32" t="s">
+      <c r="P17" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q17" s="36" t="s">
         <v>36</v>
       </c>
       <c r="R17" s="20" t="s">
@@ -2536,7 +2536,7 @@
         <v>12</v>
       </c>
       <c r="W17" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="X17" s="12" t="s">
         <v>34</v>
@@ -2551,10 +2551,10 @@
         <v>11</v>
       </c>
       <c r="AB17" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC17" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AD17" s="12" t="s">
         <v>36</v>
@@ -2567,16 +2567,16 @@
       </c>
     </row>
     <row r="18" spans="1:32" ht="12.75">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="26" t="s">
         <v>58</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="36" t="s">
         <v>59</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -2585,20 +2585,20 @@
       <c r="F18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="34" t="s">
+      <c r="G18" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="K18" s="34" t="s">
-        <v>14</v>
+      <c r="J18" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="L18" s="12" t="s">
         <v>36</v>
@@ -2609,20 +2609,20 @@
       <c r="N18" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="O18" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="P18" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q18" s="32" t="s">
+      <c r="O18" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="P18" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q18" s="36" t="s">
         <v>17</v>
       </c>
       <c r="R18" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="T18" s="20" t="s">
         <v>11</v>
@@ -2665,16 +2665,16 @@
       </c>
     </row>
     <row r="19" spans="1:32" ht="12.75">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="26" t="s">
         <v>60</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -2683,77 +2683,77 @@
       <c r="F19" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>43</v>
+      <c r="G19" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>42</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>11</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L19" s="12" t="s">
         <v>48</v>
       </c>
       <c r="M19" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="N19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O19" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q19" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="S19" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="V19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="W19" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="N19" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="O19" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="P19" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q19" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="R19" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="S19" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T19" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="V19" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>44</v>
-      </c>
       <c r="X19" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y19" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z19" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA19" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB19" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC19" s="20" t="s">
         <v>11</v>
       </c>
       <c r="AD19" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AE19" s="12" t="s">
         <v>36</v>
@@ -2763,16 +2763,16 @@
       </c>
     </row>
     <row r="20" spans="1:32" ht="12.75">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="32" t="s">
+      <c r="C20" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>36</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -2781,20 +2781,20 @@
       <c r="F20" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="32" t="s">
+      <c r="G20" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="36" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>36</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L20" s="20" t="s">
         <v>11</v>
@@ -2805,13 +2805,13 @@
       <c r="N20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O20" s="32" t="s">
+      <c r="O20" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="P20" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q20" s="32" t="s">
+      <c r="P20" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q20" s="36" t="s">
         <v>17</v>
       </c>
       <c r="R20" s="12" t="s">
@@ -2861,16 +2861,16 @@
       </c>
     </row>
     <row r="21" spans="1:32" ht="12.75">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="26" t="s">
         <v>63</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="36" t="s">
         <v>59</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -2903,20 +2903,20 @@
       <c r="N21" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="O21" s="32" t="s">
+      <c r="O21" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="P21" s="32" t="s">
+      <c r="P21" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="Q21" s="32" t="s">
+      <c r="Q21" s="36" t="s">
         <v>59</v>
       </c>
       <c r="R21" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S21" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T21" s="20" t="s">
         <v>11</v>
@@ -2946,7 +2946,7 @@
         <v>35</v>
       </c>
       <c r="AC21" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AD21" s="12" t="s">
         <v>36</v>
@@ -2959,16 +2959,16 @@
       </c>
     </row>
     <row r="22" spans="1:32" ht="12.75">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="26" t="s">
         <v>64</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="36" t="s">
         <v>65</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -2990,25 +2990,25 @@
         <v>48</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L22" s="12" t="s">
         <v>48</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N22" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O22" s="32" t="s">
+      <c r="O22" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="P22" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q22" s="32" t="s">
-        <v>43</v>
+      <c r="P22" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="36" t="s">
+        <v>42</v>
       </c>
       <c r="R22" s="12" t="s">
         <v>33</v>
@@ -3057,20 +3057,20 @@
       </c>
     </row>
     <row r="23" spans="1:32" ht="12.75">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="26" t="s">
         <v>66</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="36" t="s">
         <v>65</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>12</v>
@@ -3094,18 +3094,18 @@
         <v>34</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N23" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O23" s="32" t="s">
+      <c r="O23" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="P23" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q23" s="35" t="s">
+      <c r="P23" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q23" s="38" t="s">
         <v>36</v>
       </c>
       <c r="R23" s="12" t="s">
@@ -3115,7 +3115,7 @@
         <v>34</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U23" s="12" t="s">
         <v>17</v>
@@ -3155,16 +3155,16 @@
       </c>
     </row>
     <row r="24" spans="1:32" ht="12.75">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="26" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="36" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -3197,16 +3197,16 @@
       <c r="N24" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="O24" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="P24" s="32" t="s">
+      <c r="O24" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="P24" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="Q24" s="32" t="s">
+      <c r="Q24" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="R24" s="35" t="s">
+      <c r="R24" s="38" t="s">
         <v>18</v>
       </c>
       <c r="S24" s="20" t="s">
@@ -3236,43 +3236,43 @@
       <c r="AA24" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="AB24" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC24" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD24" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE24" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF24" s="32" t="s">
+      <c r="AB24" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC24" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD24" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE24" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF24" s="36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:32" ht="12.75">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="26" t="s">
         <v>69</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="36" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>17</v>
@@ -3281,13 +3281,13 @@
         <v>11</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K25" s="12" t="s">
         <v>14</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>36</v>
@@ -3298,10 +3298,10 @@
       <c r="O25" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P25" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25" s="35" t="s">
+      <c r="P25" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" s="38" t="s">
         <v>36</v>
       </c>
       <c r="R25" s="21" t="s">
@@ -3314,7 +3314,7 @@
         <v>18</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V25" s="20" t="s">
         <v>11</v>
@@ -3326,41 +3326,41 @@
         <v>17</v>
       </c>
       <c r="Y25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Z25" s="12" t="s">
         <v>34</v>
       </c>
       <c r="AA25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AB25" s="12" t="s">
         <v>36</v>
       </c>
       <c r="AC25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AD25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AE25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF25" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:32" ht="12.75">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="26" t="s">
         <v>70</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="C26" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="36" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -3393,19 +3393,19 @@
       <c r="N26" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="O26" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="S26" s="13" t="s">
+      <c r="O26" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="S26" s="12" t="s">
         <v>21</v>
       </c>
       <c r="T26" s="12" t="s">
@@ -3449,16 +3449,16 @@
       </c>
     </row>
     <row r="27" spans="1:32" ht="12.75">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="26" t="s">
         <v>71</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="32" t="s">
+      <c r="C27" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="36" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -3479,8 +3479,8 @@
       <c r="J27" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K27" s="12" t="s">
-        <v>17</v>
+      <c r="K27" s="40" t="s">
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="s">
         <v>34</v>
@@ -3491,13 +3491,13 @@
       <c r="N27" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="O27" s="35" t="s">
+      <c r="O27" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="P27" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q27" s="35" t="s">
+      <c r="P27" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="38" t="s">
         <v>18</v>
       </c>
       <c r="R27" s="21" t="s">
@@ -3507,7 +3507,7 @@
         <v>18</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U27" s="12" t="s">
         <v>36</v>
@@ -3516,7 +3516,7 @@
         <v>11</v>
       </c>
       <c r="W27" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="X27" s="12" t="s">
         <v>12</v>
@@ -3543,17 +3543,17 @@
         <v>36</v>
       </c>
       <c r="AF27" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:32" ht="12.75">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="26" t="s">
         <v>72</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="37" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="20" t="s">
@@ -3587,15 +3587,15 @@
         <v>11</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="O28" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="O28" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="P28" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q28" s="35" t="s">
+      <c r="P28" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q28" s="38" t="s">
         <v>36</v>
       </c>
       <c r="R28" s="21" t="s">
@@ -3629,13 +3629,13 @@
         <v>18</v>
       </c>
       <c r="AB28" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AC28" s="12" t="s">
         <v>36</v>
       </c>
       <c r="AD28" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE28" s="12" t="s">
         <v>34</v>
@@ -3645,29 +3645,29 @@
       </c>
     </row>
     <row r="29" spans="1:32" ht="12.75">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="26" t="s">
         <v>73</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>23</v>
@@ -3682,25 +3682,25 @@
         <v>14</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N29" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="O29" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="P29" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q29" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="N29" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="P29" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q29" s="36" t="s">
         <v>17</v>
       </c>
       <c r="R29" s="20" t="s">
         <v>11</v>
       </c>
       <c r="S29" s="21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T29" s="12" t="s">
         <v>12</v>
@@ -3733,7 +3733,7 @@
         <v>17</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE29" s="12" t="s">
         <v>34</v>
@@ -3743,16 +3743,16 @@
       </c>
     </row>
     <row r="30" spans="1:32" ht="12.75">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="26" t="s">
         <v>74</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="32" t="s">
+      <c r="C30" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="36" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -3768,16 +3768,16 @@
         <v>14</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>48</v>
@@ -3785,13 +3785,13 @@
       <c r="N30" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O30" s="35" t="s">
+      <c r="O30" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="P30" s="35" t="s">
+      <c r="P30" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="Q30" s="32" t="s">
+      <c r="Q30" s="36" t="s">
         <v>15</v>
       </c>
       <c r="R30" s="12" t="s">
@@ -3807,50 +3807,50 @@
         <v>11</v>
       </c>
       <c r="V30" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="X30" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z30" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA30" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE30" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="W30" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="X30" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z30" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA30" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB30" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE30" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="AF30" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:32" ht="12.75">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="26" t="s">
         <v>75</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="32" t="s">
+      <c r="C31" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="36" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -3863,7 +3863,7 @@
         <v>34</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>17</v>
@@ -3881,22 +3881,22 @@
         <v>11</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="O31" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="O31" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="P31" s="32" t="s">
+      <c r="P31" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="Q31" s="32" t="s">
+      <c r="Q31" s="36" t="s">
         <v>12</v>
       </c>
       <c r="R31" s="21" t="s">
         <v>34</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T31" s="20" t="s">
         <v>11</v>
@@ -3932,23 +3932,23 @@
         <v>34</v>
       </c>
       <c r="AE31" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AF31" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:32" ht="12.75">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="26" t="s">
         <v>76</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -3972,7 +3972,7 @@
       <c r="K32" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="L32" s="25" t="s">
+      <c r="L32" s="24" t="s">
         <v>19</v>
       </c>
       <c r="M32" s="20" t="s">
@@ -3981,23 +3981,23 @@
       <c r="N32" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O32" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="P32" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q32" s="32" t="s">
+      <c r="O32" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="P32" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q32" s="36" t="s">
         <v>17</v>
       </c>
       <c r="R32" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="S32" s="21" t="s">
         <v>17</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U32" s="20" t="s">
         <v>11</v>
@@ -4037,7 +4037,7 @@
       </c>
     </row>
     <row r="33" spans="1:32" ht="12.75">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="26" t="s">
         <v>78</v>
       </c>
       <c r="B33" s="12" t="s">
@@ -4046,47 +4046,47 @@
       <c r="C33" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="36" t="s">
         <v>34</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G33" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="N33" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="O33" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="I33" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="M33" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="N33" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="O33" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="P33" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q33" s="32" t="s">
-        <v>43</v>
+      <c r="P33" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q33" s="36" t="s">
+        <v>42</v>
       </c>
       <c r="R33" s="20" t="s">
         <v>11</v>
@@ -4128,14 +4128,14 @@
         <v>11</v>
       </c>
       <c r="AE33" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AF33" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:32" ht="12.75">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="26" t="s">
         <v>79</v>
       </c>
       <c r="B34" s="12" t="s">
@@ -4144,17 +4144,17 @@
       <c r="C34" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="36" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>14</v>
@@ -4174,17 +4174,17 @@
       <c r="M34" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N34" s="40" t="s">
+      <c r="N34" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="O34" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="P34" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q34" s="32" t="s">
-        <v>39</v>
+      <c r="O34" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="P34" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q34" s="36" t="s">
+        <v>38</v>
       </c>
       <c r="R34" s="12" t="s">
         <v>14</v>
@@ -4196,7 +4196,7 @@
         <v>14</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V34" s="12" t="s">
         <v>14</v>
@@ -4226,18 +4226,18 @@
         <v>34</v>
       </c>
       <c r="AE34" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF34" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:32" ht="12.75">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="26" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>17</v>
@@ -4245,10 +4245,10 @@
       <c r="D35" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="E35" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="38" t="s">
+      <c r="F35" s="33" t="s">
         <v>23</v>
       </c>
       <c r="G35" s="12" t="s">
@@ -4258,7 +4258,7 @@
         <v>34</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>34</v>
@@ -4276,7 +4276,7 @@
         <v>11</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P35" s="12" t="s">
         <v>36</v>
@@ -4297,7 +4297,7 @@
         <v>17</v>
       </c>
       <c r="V35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="W35" s="12" t="s">
         <v>34</v>
@@ -4306,7 +4306,7 @@
         <v>17</v>
       </c>
       <c r="Y35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z35" s="12" t="s">
         <v>12</v>
@@ -4315,23 +4315,23 @@
         <v>11</v>
       </c>
       <c r="AB35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AC35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE35" s="12" t="s">
         <v>34</v>
       </c>
       <c r="AF35" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:32" ht="12.75">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="29" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="12" t="s">
@@ -4413,16 +4413,16 @@
         <v>36</v>
       </c>
       <c r="AB36" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AC36" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD36" s="20" t="s">
         <v>11</v>
       </c>
       <c r="AE36" s="12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AF36" s="12" t="s">
         <v>34</v>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F662C2D3-B8E2-4DB8-9E90-D9B2208C797F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72BD1FC6-39AA-4559-BF19-34C9FCECD952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,91 +87,91 @@
     <t>6:00 - 14:00</t>
   </si>
   <si>
+    <t>15:00 - 22:00</t>
+  </si>
+  <si>
     <t>8:00 - 14:00</t>
   </si>
   <si>
+    <t>ANDREA CAROLINA TORRES NUÑEZ</t>
+  </si>
+  <si>
+    <t>14:00 - 22:00</t>
+  </si>
+  <si>
+    <t>14:00 - 21:00</t>
+  </si>
+  <si>
+    <t>6:00 - 12:00</t>
+  </si>
+  <si>
+    <t>16:00 - 22:00</t>
+  </si>
+  <si>
+    <t>JOSE GUILLERMO LOZANO GUERRA </t>
+  </si>
+  <si>
+    <t>11:00 - 19:00</t>
+  </si>
+  <si>
+    <t>13:00 - 19:00</t>
+  </si>
+  <si>
+    <t>12:00 - 18:00</t>
+  </si>
+  <si>
+    <t>Salario Emocional</t>
+  </si>
+  <si>
+    <t>21:00 - 6:00</t>
+  </si>
+  <si>
+    <t>22:00 - 6:00</t>
+  </si>
+  <si>
+    <t>JURANI ROSAS</t>
+  </si>
+  <si>
+    <t>14:30 - 22:00</t>
+  </si>
+  <si>
+    <t>JHON HENRY MARIN SANTOFIMIO</t>
+  </si>
+  <si>
+    <t>8:00 - 16:00</t>
+  </si>
+  <si>
+    <t>NATALIA CARRILLO HERNANDEZ</t>
+  </si>
+  <si>
+    <t>15:00 - 21:00</t>
+  </si>
+  <si>
+    <t>8:00 - 15:00</t>
+  </si>
+  <si>
+    <t>FABER SEBASTIAN FÚQUENE HERNANDEZ</t>
+  </si>
+  <si>
+    <t>9:00 - 17:00</t>
+  </si>
+  <si>
+    <t>Backup</t>
+  </si>
+  <si>
+    <t>FREDY ALEXANDER CALCETERO PARDO</t>
+  </si>
+  <si>
+    <t>7:00 - 15:00</t>
+  </si>
+  <si>
+    <t>9:00 - 15:00</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID CHAPARRO VARGAS</t>
+  </si>
+  <si>
     <t>7:00 - 14:00</t>
-  </si>
-  <si>
-    <t>ANDREA CAROLINA TORRES NUÑEZ</t>
-  </si>
-  <si>
-    <t>14:00 - 22:00</t>
-  </si>
-  <si>
-    <t>15:00 - 22:00</t>
-  </si>
-  <si>
-    <t>14:00 - 21:00</t>
-  </si>
-  <si>
-    <t>6:00 - 12:00</t>
-  </si>
-  <si>
-    <t>16:00 - 22:00</t>
-  </si>
-  <si>
-    <t>JOSE GUILLERMO LOZANO GUERRA </t>
-  </si>
-  <si>
-    <t>11:00 - 19:00</t>
-  </si>
-  <si>
-    <t>13:00 - 19:00</t>
-  </si>
-  <si>
-    <t>12:00 - 18:00</t>
-  </si>
-  <si>
-    <t>Salario Emocional</t>
-  </si>
-  <si>
-    <t>21:00 - 6:00</t>
-  </si>
-  <si>
-    <t>22:00 - 6:00</t>
-  </si>
-  <si>
-    <t>JURANI ROSAS</t>
-  </si>
-  <si>
-    <t>14:30 - 22:00</t>
-  </si>
-  <si>
-    <t>JHON HENRY MARIN SANTOFIMIO</t>
-  </si>
-  <si>
-    <t>8:00 - 16:00</t>
-  </si>
-  <si>
-    <t>NATALIA CARRILLO HERNANDEZ</t>
-  </si>
-  <si>
-    <t>15:00 - 21:00</t>
-  </si>
-  <si>
-    <t>8:00 - 15:00</t>
-  </si>
-  <si>
-    <t>FABER SEBASTIAN FÚQUENE HERNANDEZ</t>
-  </si>
-  <si>
-    <t>9:00 - 17:00</t>
-  </si>
-  <si>
-    <t>Backup</t>
-  </si>
-  <si>
-    <t>FREDY ALEXANDER CALCETERO PARDO</t>
-  </si>
-  <si>
-    <t>7:00 - 15:00</t>
-  </si>
-  <si>
-    <t>9:00 - 15:00</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID CHAPARRO VARGAS</t>
   </si>
   <si>
     <t>9:00 - 16:00</t>
@@ -283,7 +283,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -341,19 +341,25 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Aptos"/>
+      <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -414,8 +420,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1F0C8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -499,17 +523,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,7 +550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -567,32 +600,38 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1042,41 +1081,41 @@
       <c r="S3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="17" t="s">
+      <c r="T3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="18" t="s">
+      <c r="U3" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="V3" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y3" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="W3" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="X3" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y3" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD3" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE3" s="21" t="s">
-        <v>17</v>
+      <c r="AD3" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="30" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="12.75">
@@ -1096,174 +1135,174 @@
         <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="22" t="s">
+      <c r="Q4" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="R4" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="S4" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="U4" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="V4" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="W4" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="23" t="s">
+      <c r="X4" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="23" t="s">
+      <c r="Y4" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z4" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="Q4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R4" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="S4" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="U4" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="V4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="W4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X4" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z4" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB4" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC4" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE4" s="23" t="s">
+      <c r="AD4" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE4" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="12.75">
       <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="16" t="s">
+      <c r="N5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="17" t="s">
+      <c r="O5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="P5" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="R5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="R5" s="19" t="s">
-        <v>29</v>
-      </c>
       <c r="S5" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="T5" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="U5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="W5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="X5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD5" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="T5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="V5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC5" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD5" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE5" s="20" t="s">
         <v>10</v>
@@ -1271,7 +1310,7 @@
     </row>
     <row r="6" spans="1:31" ht="12.75">
       <c r="A6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
@@ -1301,16 +1340,16 @@
         <v>15</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="26" t="s">
-        <v>32</v>
+        <v>16</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="O6" s="17" t="s">
         <v>19</v>
@@ -1327,38 +1366,38 @@
       <c r="S6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T6" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="U6" s="17" t="s">
+      <c r="T6" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="V6" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="W6" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="X6" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB6" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC6" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD6" s="17" t="s">
-        <v>10</v>
+      <c r="U6" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="V6" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="W6" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X6" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD6" s="29" t="s">
+        <v>20</v>
       </c>
       <c r="AE6" s="17" t="s">
         <v>12</v>
@@ -1366,55 +1405,55 @@
     </row>
     <row r="7" spans="1:31" ht="12.75">
       <c r="A7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>33</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="28" t="s">
-        <v>29</v>
+        <v>29</v>
+      </c>
+      <c r="Q7" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="R7" s="17" t="s">
         <v>10</v>
@@ -1422,38 +1461,38 @@
       <c r="S7" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="T7" s="19" t="s">
+      <c r="T7" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U7" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="V7" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W7" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="X7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="U7" s="19" t="s">
+      <c r="Z7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="V7" s="19" t="s">
+      <c r="AA7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="W7" s="19" t="s">
+      <c r="AB7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="X7" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD7" s="19" t="s">
-        <v>13</v>
+      <c r="AC7" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD7" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE7" s="20" t="s">
         <v>10</v>
@@ -1461,31 +1500,31 @@
     </row>
     <row r="8" spans="1:31" ht="12.75">
       <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="H8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>11</v>
@@ -1494,61 +1533,61 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="26" t="s">
+      <c r="O8" s="24" t="s">
         <v>11</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="26" t="s">
+      <c r="R8" s="24" t="s">
         <v>10</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="T8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="V8" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="W8" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="X8" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y8" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z8" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA8" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB8" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC8" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD8" s="17" t="s">
-        <v>37</v>
+        <v>22</v>
+      </c>
+      <c r="T8" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="V8" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W8" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X8" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y8" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA8" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB8" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC8" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD8" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE8" s="17" t="s">
         <v>10</v>
@@ -1556,7 +1595,7 @@
     </row>
     <row r="9" spans="1:31" ht="12.75">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -1568,81 +1607,81 @@
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="R9" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T9" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q9" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S9" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="U9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="V9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="W9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="X9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD9" s="25" t="s">
+      <c r="U9" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="V9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="W9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y9" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z9" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA9" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB9" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD9" s="27" t="s">
         <v>10</v>
       </c>
       <c r="AE9" s="18" t="s">
@@ -1651,32 +1690,32 @@
     </row>
     <row r="10" spans="1:31" ht="12.75">
       <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="J10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1684,13 +1723,13 @@
         <v>19</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="N10" s="26" t="s">
-        <v>20</v>
+      <c r="N10" s="24" t="s">
+        <v>16</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>11</v>
@@ -1707,38 +1746,38 @@
       <c r="S10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="U10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="W10" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="X10" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z10" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD10" s="17" t="s">
-        <v>15</v>
+      <c r="T10" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="U10" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="V10" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="X10" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z10" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA10" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB10" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC10" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD10" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE10" s="17" t="s">
         <v>10</v>
@@ -1746,46 +1785,46 @@
     </row>
     <row r="11" spans="1:31" ht="12.75">
       <c r="A11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="N11" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O11" s="17" t="s">
         <v>12</v>
@@ -1793,47 +1832,47 @@
       <c r="P11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q11" s="26" t="s">
-        <v>21</v>
+      <c r="Q11" s="24" t="s">
+        <v>20</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S11" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="T11" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="U11" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="V11" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="W11" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X11" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="T11" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="U11" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="V11" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="W11" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="X11" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y11" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z11" s="17" t="s">
+      <c r="Y11" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="AA11" s="17" t="s">
+      <c r="Z11" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="AB11" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC11" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD11" s="17" t="s">
-        <v>19</v>
+      <c r="AA11" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB11" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC11" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD11" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE11" s="17" t="s">
         <v>10</v>
@@ -1844,7 +1883,7 @@
         <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
@@ -1853,17 +1892,17 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="I12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1871,22 +1910,22 @@
         <v>10</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>47</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q12" s="17" t="s">
         <v>10</v>
@@ -1897,38 +1936,38 @@
       <c r="S12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U12" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="V12" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="W12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="X12" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y12" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA12" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB12" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC12" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD12" s="17" t="s">
-        <v>39</v>
+      <c r="T12" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="U12" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="V12" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W12" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="X12" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y12" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z12" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA12" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB12" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC12" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD12" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE12" s="17" t="s">
         <v>10</v>
@@ -1939,7 +1978,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>45</v>
@@ -1948,10 +1987,10 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>19</v>
@@ -1966,64 +2005,64 @@
         <v>15</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="S13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T13" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U13" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="V13" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="W13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="X13" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y13" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z13" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA13" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N13" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="O13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="T13" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="U13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="V13" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="W13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="X13" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z13" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB13" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC13" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD13" s="17" t="s">
-        <v>10</v>
+      <c r="AC13" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD13" s="27" t="s">
+        <v>12</v>
       </c>
       <c r="AE13" s="17" t="s">
         <v>12</v>
@@ -2034,7 +2073,7 @@
         <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
@@ -2043,10 +2082,10 @@
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>11</v>
@@ -2064,16 +2103,16 @@
         <v>19</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="24" t="s">
+      <c r="N14" s="23" t="s">
         <v>50</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P14" s="17" t="s">
         <v>19</v>
@@ -2082,43 +2121,43 @@
         <v>10</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="U14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="V14" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="W14" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="X14" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y14" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z14" s="17" t="s">
+      <c r="T14" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="U14" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="V14" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="W14" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="AA14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD14" s="17" t="s">
-        <v>19</v>
+      <c r="Y14" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z14" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA14" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB14" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD14" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="17" t="s">
         <v>10</v>
@@ -2132,43 +2171,43 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P15" s="17" t="s">
         <v>10</v>
@@ -2177,46 +2216,46 @@
         <v>10</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="T15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="U15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="V15" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="W15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="X15" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD15" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="T15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="U15" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="V15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="W15" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="X15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD15" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="AE15" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="12.75">
@@ -2224,94 +2263,94 @@
         <v>52</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q16" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R16" s="17" t="s">
         <v>10</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="V16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="W16" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="X16" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD16" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="T16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="U16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="V16" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="W16" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="X16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD16" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="AE16" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="12.75">
@@ -2319,7 +2358,7 @@
         <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
@@ -2328,34 +2367,34 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O17" s="17" t="s">
         <v>15</v>
@@ -2367,43 +2406,43 @@
         <v>10</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V17" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="W17" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="X17" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y17" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z17" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA17" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB17" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC17" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD17" s="17" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="T17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="U17" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="V17" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X17" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y17" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z17" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA17" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB17" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC17" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD17" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE17" s="17" t="s">
         <v>10</v>
@@ -2414,94 +2453,94 @@
         <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q18" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="R18" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="U18" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="V18" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W18" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="X18" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y18" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z18" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA18" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB18" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC18" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD18" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="AE18" s="17" t="s">
         <v>42</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q18" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="V18" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="W18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="X18" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y18" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z18" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA18" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB18" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC18" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD18" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE18" s="17" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="12.75">
@@ -2509,10 +2548,10 @@
         <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -2536,64 +2575,64 @@
         <v>10</v>
       </c>
       <c r="K19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="R19" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="R19" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="S19" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="T19" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="V19" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="W19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="X19" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD19" s="17" t="s">
-        <v>10</v>
+      <c r="T19" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="U19" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="V19" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W19" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X19" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y19" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z19" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA19" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB19" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC19" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD19" s="27" t="s">
+        <v>15</v>
       </c>
       <c r="AE19" s="17" t="s">
         <v>15</v>
@@ -2604,40 +2643,40 @@
         <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>19</v>
@@ -2655,40 +2694,40 @@
         <v>10</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="T20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="T20" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="U20" s="17" t="s">
+      <c r="U20" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="V20" s="17" t="s">
+      <c r="V20" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="W20" s="17" t="s">
+      <c r="W20" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="X20" s="17" t="s">
+      <c r="X20" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Y20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z20" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA20" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB20" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC20" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD20" s="18" t="s">
-        <v>39</v>
+      <c r="Y20" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z20" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA20" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB20" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC20" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD20" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE20" s="20" t="s">
         <v>10</v>
@@ -2699,94 +2738,94 @@
         <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="T21" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="U21" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="V21" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="W21" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="X21" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y21" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z21" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="N21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="O21" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="P21" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q21" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="R21" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="S21" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="T21" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="U21" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="V21" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="W21" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="X21" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y21" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z21" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA21" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB21" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD21" s="17" t="s">
-        <v>10</v>
+      <c r="AA21" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB21" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC21" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD21" s="27" t="s">
+        <v>35</v>
       </c>
       <c r="AE21" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="12.75">
@@ -2794,7 +2833,7 @@
         <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
@@ -2803,33 +2842,33 @@
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="M22" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="24" t="s">
         <v>61</v>
       </c>
       <c r="O22" s="17" t="s">
@@ -2842,43 +2881,43 @@
         <v>10</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="T22" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="U22" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="V22" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="W22" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="X22" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA22" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC22" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD22" s="17" t="s">
-        <v>10</v>
+        <v>36</v>
+      </c>
+      <c r="T22" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="U22" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="V22" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X22" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y22" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z22" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA22" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB22" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC22" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD22" s="27" t="s">
+        <v>11</v>
       </c>
       <c r="AE22" s="17" t="s">
         <v>11</v>
@@ -2898,40 +2937,40 @@
         <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="O23" s="17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q23" s="17" t="s">
         <v>10</v>
@@ -2940,40 +2979,40 @@
         <v>63</v>
       </c>
       <c r="S23" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="T23" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="U23" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="V23" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="W23" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X23" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="T23" s="17" t="s">
+      <c r="Y23" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="U23" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="V23" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="W23" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="X23" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y23" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z23" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA23" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB23" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC23" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD23" s="17" t="s">
-        <v>11</v>
+      <c r="Z23" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA23" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB23" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC23" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD23" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE23" s="17" t="s">
         <v>10</v>
@@ -2987,7 +3026,7 @@
         <v>15</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -2996,7 +3035,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>19</v>
@@ -3014,7 +3053,7 @@
         <v>15</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>45</v>
@@ -3029,46 +3068,46 @@
         <v>10</v>
       </c>
       <c r="Q24" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T24" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U24" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="V24" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="W24" s="17" t="s">
+      <c r="T24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="X24" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y24" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z24" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA24" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB24" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC24" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD24" s="17" t="s">
-        <v>42</v>
+      <c r="U24" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="V24" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="W24" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X24" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y24" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z24" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA24" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB24" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC24" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE24" s="17" t="s">
         <v>10</v>
@@ -3082,7 +3121,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -3112,19 +3151,19 @@
         <v>19</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N25" s="17" t="s">
         <v>45</v>
       </c>
       <c r="O25" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P25" s="17" t="s">
         <v>12</v>
       </c>
       <c r="Q25" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R25" s="17" t="s">
         <v>10</v>
@@ -3132,41 +3171,41 @@
       <c r="S25" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T25" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U25" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="V25" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="W25" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="X25" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y25" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z25" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA25" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB25" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC25" s="17" t="s">
+      <c r="T25" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U25" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="V25" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W25" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB25" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="AD25" s="17" t="s">
-        <v>43</v>
+      <c r="AC25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD25" s="27" t="s">
+        <v>36</v>
       </c>
       <c r="AE25" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="12.75">
@@ -3174,7 +3213,7 @@
         <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
@@ -3195,13 +3234,13 @@
         <v>15</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>10</v>
@@ -3209,14 +3248,14 @@
       <c r="M26" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N26" s="26" t="s">
+      <c r="N26" s="24" t="s">
         <v>50</v>
       </c>
       <c r="O26" s="17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q26" s="17" t="s">
         <v>12</v>
@@ -3227,38 +3266,38 @@
       <c r="S26" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="T26" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="U26" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="V26" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="W26" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="X26" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD26" s="17" t="s">
-        <v>19</v>
+      <c r="T26" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="U26" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="V26" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="W26" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="X26" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y26" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z26" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA26" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB26" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC26" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD26" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE26" s="17" t="s">
         <v>10</v>
@@ -3269,91 +3308,91 @@
         <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>68</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>15</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O27" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q27" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R27" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T27" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="U27" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="V27" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="W27" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="X27" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y27" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="Z27" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA27" s="17" t="s">
+      <c r="T27" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U27" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="AB27" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC27" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD27" s="17" t="s">
+      <c r="V27" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="W27" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X27" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y27" s="27" t="s">
         <v>20</v>
+      </c>
+      <c r="Z27" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA27" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB27" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC27" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD27" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE27" s="17" t="s">
         <v>10</v>
@@ -3385,28 +3424,28 @@
         <v>10</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M28" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O28" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q28" s="17" t="s">
         <v>10</v>
@@ -3417,41 +3456,41 @@
       <c r="S28" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="T28" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="U28" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="V28" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="W28" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="X28" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y28" s="17" t="s">
+      <c r="T28" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="U28" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="V28" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="W28" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X28" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y28" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z28" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA28" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB28" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC28" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="Z28" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA28" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB28" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC28" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD28" s="29" t="s">
-        <v>16</v>
+      <c r="AD28" s="27" t="s">
+        <v>36</v>
       </c>
       <c r="AE28" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="12.75">
@@ -3459,91 +3498,91 @@
         <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="O29" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P29" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q29" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="O29" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="P29" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q29" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="R29" s="17" t="s">
         <v>10</v>
       </c>
       <c r="S29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="U29" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="V29" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="W29" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="X29" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y29" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z29" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB29" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD29" s="17" t="s">
-        <v>21</v>
+      <c r="T29" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="U29" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="V29" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="W29" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="X29" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y29" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z29" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA29" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB29" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC29" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD29" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE29" s="17" t="s">
         <v>10</v>
@@ -3572,10 +3611,10 @@
         <v>15</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>10</v>
@@ -3593,7 +3632,7 @@
         <v>12</v>
       </c>
       <c r="O30" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P30" s="17" t="s">
         <v>10</v>
@@ -3602,43 +3641,43 @@
         <v>15</v>
       </c>
       <c r="R30" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="T30" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="U30" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V30" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="W30" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="X30" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y30" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z30" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA30" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB30" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC30" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD30" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="T30" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="U30" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="V30" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="W30" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X30" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y30" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z30" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA30" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB30" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC30" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD30" s="27" t="s">
+        <v>19</v>
       </c>
       <c r="AE30" s="17" t="s">
         <v>19</v>
@@ -3652,22 +3691,22 @@
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>11</v>
@@ -3676,7 +3715,7 @@
         <v>10</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>15</v>
@@ -3702,41 +3741,41 @@
       <c r="S31" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="T31" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="U31" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="V31" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="W31" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="X31" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y31" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z31" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA31" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB31" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC31" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD31" s="17" t="s">
-        <v>20</v>
+      <c r="T31" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="U31" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="V31" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="W31" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X31" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y31" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z31" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA31" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB31" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC31" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD31" s="27" t="s">
+        <v>35</v>
       </c>
       <c r="AE31" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="12.75">
@@ -3744,13 +3783,13 @@
         <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>19</v>
@@ -3765,19 +3804,19 @@
         <v>19</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N32" s="17" t="s">
         <v>10</v>
@@ -3786,10 +3825,10 @@
         <v>19</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q32" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R32" s="17" t="s">
         <v>74</v>
@@ -3797,38 +3836,38 @@
       <c r="S32" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T32" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="U32" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="V32" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="W32" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="X32" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y32" s="17" t="s">
+      <c r="T32" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U32" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="V32" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="W32" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="X32" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="Z32" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA32" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB32" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC32" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD32" s="17" t="s">
-        <v>42</v>
+      <c r="Y32" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA32" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB32" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC32" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD32" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE32" s="17" t="s">
         <v>10</v>
@@ -3842,91 +3881,91 @@
         <v>19</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="R33" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S33" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T33" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="U33" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="V33" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W33" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="X33" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y33" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z33" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA33" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB33" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="O33" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="P33" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="R33" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S33" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="T33" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="U33" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="V33" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="W33" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="X33" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y33" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z33" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA33" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB33" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC33" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD33" s="17" t="s">
-        <v>21</v>
+      <c r="AD33" s="27" t="s">
+        <v>35</v>
       </c>
       <c r="AE33" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="12.75">
@@ -3937,25 +3976,25 @@
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>10</v>
@@ -3973,13 +4012,13 @@
         <v>10</v>
       </c>
       <c r="O34" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q34" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R34" s="17" t="s">
         <v>10</v>
@@ -3987,38 +4026,38 @@
       <c r="S34" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T34" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="U34" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="V34" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="W34" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="X34" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y34" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z34" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA34" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB34" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC34" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD34" s="17" t="s">
-        <v>37</v>
+      <c r="T34" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="U34" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="V34" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="W34" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X34" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y34" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z34" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA34" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB34" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC34" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD34" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE34" s="17" t="s">
         <v>10</v>
@@ -4041,31 +4080,31 @@
         <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N35" s="26" t="s">
-        <v>32</v>
+      <c r="N35" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="O35" s="17" t="s">
         <v>19</v>
@@ -4074,46 +4113,46 @@
         <v>10</v>
       </c>
       <c r="Q35" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R35" s="17" t="s">
         <v>15</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="T35" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="U35" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="V35" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="W35" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="X35" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y35" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z35" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA35" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB35" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC35" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD35" s="17" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="T35" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="U35" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="V35" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="W35" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="X35" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y35" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z35" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA35" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB35" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC35" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD35" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE35" s="17" t="s">
         <v>10</v>
@@ -4127,7 +4166,7 @@
         <v>19</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
@@ -4145,7 +4184,7 @@
         <v>15</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>15</v>
@@ -4160,16 +4199,16 @@
         <v>10</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O36" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="Q36" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R36" s="17" t="s">
         <v>10</v>
@@ -4177,38 +4216,38 @@
       <c r="S36" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="T36" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="U36" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="V36" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="W36" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="X36" s="17" t="s">
+      <c r="T36" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="U36" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="V36" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="W36" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="X36" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="Y36" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z36" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA36" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB36" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC36" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD36" s="17" t="s">
-        <v>15</v>
+      <c r="Y36" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z36" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA36" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB36" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC36" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD36" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AE36" s="17" t="s">
         <v>10</v>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72BD1FC6-39AA-4559-BF19-34C9FCECD952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56DB66EA-ABCE-43A4-9643-58A7E169555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="81">
   <si>
     <t>Sabado</t>
   </si>
@@ -225,12 +225,12 @@
     <t>13:30 - 21:00</t>
   </si>
   <si>
+    <t>13:00 - 20:00</t>
+  </si>
+  <si>
     <t>NICOLAS JOSE CABANZO SANTOS</t>
   </si>
   <si>
-    <t>13:00 - 20:00</t>
-  </si>
-  <si>
     <t>BRIAM ERNESTO NIETO HERNANDEZ</t>
   </si>
   <si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>EDGAR ALEJANDRO HERRERA SARMIENTO</t>
+  </si>
+  <si>
+    <t>descanso</t>
+  </si>
+  <si>
+    <t>14:00-22:00</t>
   </si>
   <si>
     <t>ANA MARIA CAUSIL GARCIA</t>
@@ -341,25 +347,25 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,26 +426,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1F0C8"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -523,26 +511,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -600,38 +579,53 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1081,40 +1075,40 @@
       <c r="S3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="27" t="s">
+      <c r="T3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="V3" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="W3" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X3" s="29" t="s">
+      <c r="U3" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="V3" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="Y3" s="27" t="s">
+      <c r="Y3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="Z3" s="27" t="s">
+      <c r="Z3" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="27" t="s">
+      <c r="AA3" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="AB3" s="27" t="s">
+      <c r="AB3" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="AC3" s="27" t="s">
+      <c r="AC3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="AD3" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE3" s="30" t="s">
+      <c r="AD3" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="33" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1155,61 +1149,61 @@
       <c r="L4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="22" t="s">
+      <c r="N4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="22" t="s">
+      <c r="O4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="Q4" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="R4" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="S4" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" s="30" t="s">
+      <c r="Q4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="S4" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="V4" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="W4" s="29" t="s">
+      <c r="V4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="X4" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="X4" s="29" t="s">
+      <c r="Y4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="Y4" s="29" t="s">
+      <c r="Z4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="29" t="s">
+      <c r="AA4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB4" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC4" s="30" t="s">
+      <c r="AB4" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="AD4" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE4" s="22" t="s">
+      <c r="AE4" s="20" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1271,38 +1265,38 @@
       <c r="S5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="T5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="U5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="V5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="W5" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC5" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD5" s="28" t="s">
-        <v>10</v>
+      <c r="T5" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="X5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD5" s="18" t="s">
+        <v>29</v>
       </c>
       <c r="AE5" s="20" t="s">
         <v>10</v>
@@ -1348,7 +1342,7 @@
       <c r="M6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="24" t="s">
+      <c r="N6" s="26" t="s">
         <v>31</v>
       </c>
       <c r="O6" s="17" t="s">
@@ -1366,41 +1360,41 @@
       <c r="S6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T6" s="29" t="s">
+      <c r="T6" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="U6" s="29" t="s">
+      <c r="U6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="V6" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="W6" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC6" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD6" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE6" s="17" t="s">
-        <v>12</v>
+      <c r="W6" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="X6" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA6" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="12.75">
@@ -1440,7 +1434,7 @@
       <c r="L7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="27" t="s">
         <v>33</v>
       </c>
       <c r="N7" s="19" t="s">
@@ -1452,7 +1446,7 @@
       <c r="P7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="Q7" s="28" t="s">
         <v>28</v>
       </c>
       <c r="R7" s="17" t="s">
@@ -1461,38 +1455,38 @@
       <c r="S7" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="T7" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U7" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="V7" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W7" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="X7" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="27" t="s">
+      <c r="T7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="U7" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="V7" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="W7" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="X7" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Z7" s="27" t="s">
+      <c r="AA7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="AA7" s="27" t="s">
+      <c r="AB7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="AB7" s="27" t="s">
+      <c r="AC7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="AC7" s="27" t="s">
-        <v>15</v>
-      </c>
       <c r="AD7" s="28" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE7" s="20" t="s">
         <v>10</v>
@@ -1541,7 +1535,7 @@
       <c r="N8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="24" t="s">
+      <c r="O8" s="26" t="s">
         <v>11</v>
       </c>
       <c r="P8" s="17" t="s">
@@ -1550,44 +1544,44 @@
       <c r="Q8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="24" t="s">
+      <c r="R8" s="26" t="s">
         <v>10</v>
       </c>
       <c r="S8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="T8" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="V8" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W8" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X8" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y8" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z8" s="27" t="s">
+      <c r="T8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="V8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="W8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="AA8" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB8" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC8" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD8" s="28" t="s">
-        <v>10</v>
+      <c r="AB8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD8" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="AE8" s="17" t="s">
         <v>10</v>
@@ -1651,37 +1645,37 @@
       <c r="S9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="27" t="s">
+      <c r="T9" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="U9" s="27" t="s">
+      <c r="U9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="V9" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="W9" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X9" s="27" t="s">
+      <c r="V9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Y9" s="27" t="s">
+      <c r="W9" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Z9" s="27" t="s">
+      <c r="Z9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="AA9" s="27" t="s">
+      <c r="AA9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="AB9" s="27" t="s">
+      <c r="AB9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="AC9" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD9" s="27" t="s">
+      <c r="AC9" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD9" s="25" t="s">
         <v>10</v>
       </c>
       <c r="AE9" s="18" t="s">
@@ -1728,7 +1722,7 @@
       <c r="M10" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="N10" s="24" t="s">
+      <c r="N10" s="26" t="s">
         <v>16</v>
       </c>
       <c r="O10" s="17" t="s">
@@ -1746,38 +1740,38 @@
       <c r="S10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="U10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="V10" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="W10" s="27" t="s">
+      <c r="T10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="U10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="V10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="W10" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="X10" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="X10" s="27" t="s">
+      <c r="Y10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Y10" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z10" s="27" t="s">
+      <c r="Z10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AA10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD10" s="28" t="s">
-        <v>10</v>
+      <c r="AB10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD10" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="AE10" s="17" t="s">
         <v>10</v>
@@ -1832,7 +1826,7 @@
       <c r="P11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q11" s="24" t="s">
+      <c r="Q11" s="26" t="s">
         <v>20</v>
       </c>
       <c r="R11" s="17" t="s">
@@ -1841,38 +1835,38 @@
       <c r="S11" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="T11" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="U11" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="V11" s="27" t="s">
+      <c r="T11" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="V11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="W11" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X11" s="27" t="s">
+      <c r="X11" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="Y11" s="27" t="s">
+      <c r="Z11" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="Z11" s="27" t="s">
+      <c r="AA11" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="AA11" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB11" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC11" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD11" s="28" t="s">
-        <v>10</v>
+      <c r="AB11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD11" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="AE11" s="17" t="s">
         <v>10</v>
@@ -1936,38 +1930,38 @@
       <c r="S12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T12" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="U12" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="V12" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W12" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="X12" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y12" s="27" t="s">
+      <c r="T12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="V12" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="W12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X12" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="Z12" s="27" t="s">
+      <c r="AA12" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="AA12" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB12" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC12" s="27" t="s">
+      <c r="AB12" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC12" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD12" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="AD12" s="28" t="s">
-        <v>10</v>
       </c>
       <c r="AE12" s="17" t="s">
         <v>10</v>
@@ -2013,7 +2007,7 @@
       <c r="M13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="26" t="s">
         <v>31</v>
       </c>
       <c r="O13" s="17" t="s">
@@ -2031,41 +2025,41 @@
       <c r="S13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T13" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U13" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="V13" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="W13" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="X13" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y13" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z13" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA13" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB13" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC13" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD13" s="27" t="s">
-        <v>12</v>
+      <c r="T13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="U13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="V13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="W13" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="X13" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD13" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="AE13" s="17" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="12.75">
@@ -2108,7 +2102,7 @@
       <c r="M14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="23" t="s">
+      <c r="N14" s="24" t="s">
         <v>50</v>
       </c>
       <c r="O14" s="17" t="s">
@@ -2126,38 +2120,38 @@
       <c r="S14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T14" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="U14" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="V14" s="28" t="s">
+      <c r="T14" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="U14" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="V14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="W14" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="W14" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X14" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y14" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z14" s="27" t="s">
+      <c r="X14" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z14" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="AA14" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB14" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC14" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD14" s="28" t="s">
-        <v>10</v>
+      <c r="AB14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD14" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="AE14" s="17" t="s">
         <v>10</v>
@@ -2221,38 +2215,38 @@
       <c r="S15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="T15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="U15" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="V15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="W15" s="27" t="s">
+      <c r="T15" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="U15" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="V15" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="W15" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="X15" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="X15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC15" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD15" s="27" t="s">
-        <v>28</v>
+      <c r="Y15" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z15" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA15" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB15" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC15" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD15" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="AE15" s="17" t="s">
         <v>29</v>
@@ -2316,38 +2310,38 @@
       <c r="S16" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="T16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="U16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="V16" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="W16" s="27" t="s">
+      <c r="T16" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="U16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="V16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="W16" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="X16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="X16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC16" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD16" s="27" t="s">
-        <v>28</v>
+      <c r="Y16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD16" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="AE16" s="17" t="s">
         <v>29</v>
@@ -2411,38 +2405,38 @@
       <c r="S17" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="T17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="U17" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="V17" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="W17" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X17" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y17" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z17" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA17" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB17" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC17" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD17" s="28" t="s">
-        <v>10</v>
+      <c r="T17" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="U17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="V17" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="W17" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="X17" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD17" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="AE17" s="17" t="s">
         <v>10</v>
@@ -2506,38 +2500,38 @@
       <c r="S18" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T18" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="U18" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="V18" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W18" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="X18" s="27" t="s">
+      <c r="T18" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="V18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="W18" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="Y18" s="27" t="s">
+      <c r="Z18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="Z18" s="27" t="s">
+      <c r="AA18" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="AA18" s="27" t="s">
+      <c r="AB18" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="AB18" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC18" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD18" s="27" t="s">
-        <v>42</v>
+      <c r="AC18" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD18" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="AE18" s="17" t="s">
         <v>42</v>
@@ -2583,7 +2577,7 @@
       <c r="M19" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="N19" s="24" t="s">
+      <c r="N19" s="26" t="s">
         <v>50</v>
       </c>
       <c r="O19" s="17" t="s">
@@ -2601,38 +2595,38 @@
       <c r="S19" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="T19" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="U19" s="27" t="s">
+      <c r="T19" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="V19" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="V19" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W19" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X19" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y19" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z19" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA19" s="27" t="s">
+      <c r="W19" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB19" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="AB19" s="27" t="s">
+      <c r="AC19" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="AC19" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD19" s="27" t="s">
-        <v>15</v>
+      <c r="AD19" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="AE19" s="17" t="s">
         <v>15</v>
@@ -2696,38 +2690,38 @@
       <c r="S20" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="T20" s="27" t="s">
+      <c r="T20" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="U20" s="27" t="s">
+      <c r="U20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="V20" s="27" t="s">
+      <c r="V20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="W20" s="27" t="s">
+      <c r="W20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="X20" s="27" t="s">
+      <c r="X20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="Y20" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z20" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA20" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB20" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC20" s="27" t="s">
+      <c r="Y20" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC20" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD20" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="AD20" s="28" t="s">
-        <v>10</v>
       </c>
       <c r="AE20" s="20" t="s">
         <v>10</v>
@@ -2773,7 +2767,7 @@
       <c r="M21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="N21" s="24" t="s">
+      <c r="N21" s="26" t="s">
         <v>31</v>
       </c>
       <c r="O21" s="17" t="s">
@@ -2785,44 +2779,44 @@
       <c r="Q21" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="R21" s="24" t="s">
+      <c r="R21" s="26" t="s">
         <v>10</v>
       </c>
       <c r="S21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="T21" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="U21" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="V21" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="W21" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="X21" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y21" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z21" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA21" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB21" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC21" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD21" s="27" t="s">
-        <v>35</v>
+      <c r="T21" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="V21" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="W21" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="X21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y21" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z21" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB21" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD21" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="AE21" s="17" t="s">
         <v>35</v>
@@ -2868,7 +2862,7 @@
       <c r="M22" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="24" t="s">
+      <c r="N22" s="26" t="s">
         <v>61</v>
       </c>
       <c r="O22" s="17" t="s">
@@ -2886,38 +2880,38 @@
       <c r="S22" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="T22" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="U22" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="V22" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="W22" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X22" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y22" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z22" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA22" s="27" t="s">
+      <c r="T22" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="U22" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="V22" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="W22" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="X22" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB22" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AB22" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC22" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD22" s="27" t="s">
-        <v>11</v>
+      <c r="AC22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD22" s="17" t="s">
+        <v>10</v>
       </c>
       <c r="AE22" s="17" t="s">
         <v>11</v>
@@ -2925,7 +2919,7 @@
     </row>
     <row r="23" spans="1:31" ht="12.75">
       <c r="A23" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>45</v>
@@ -2976,43 +2970,43 @@
         <v>10</v>
       </c>
       <c r="R23" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="T23" s="27" t="s">
+      <c r="T23" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="U23" s="27" t="s">
+      <c r="U23" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="V23" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="V23" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="W23" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X23" s="27" t="s">
+      <c r="W23" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="X23" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="Y23" s="27" t="s">
+      <c r="Z23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="Z23" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA23" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB23" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC23" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD23" s="28" t="s">
-        <v>10</v>
+      <c r="AA23" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB23" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC23" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD23" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="AE23" s="17" t="s">
         <v>10</v>
@@ -3076,38 +3070,38 @@
       <c r="S24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T24" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="U24" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="V24" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="W24" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X24" s="27" t="s">
+      <c r="T24" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="V24" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="W24" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="X24" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="Y24" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z24" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA24" s="27" t="s">
+      <c r="Z24" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA24" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="AB24" s="27" t="s">
+      <c r="AC24" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="AC24" s="27" t="s">
+      <c r="AD24" s="17" t="s">
         <v>41</v>
-      </c>
-      <c r="AD24" s="28" t="s">
-        <v>10</v>
       </c>
       <c r="AE24" s="17" t="s">
         <v>10</v>
@@ -3171,38 +3165,38 @@
       <c r="S25" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T25" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U25" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="V25" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W25" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X25" s="27" t="s">
+      <c r="T25" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U25" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="V25" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="W25" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X25" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="Y25" s="27" t="s">
+      <c r="Z25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="Z25" s="27" t="s">
+      <c r="AA25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="AA25" s="27" t="s">
+      <c r="AB25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="AB25" s="27" t="s">
+      <c r="AC25" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="AC25" s="27" t="s">
+      <c r="AD25" s="17" t="s">
         <v>42</v>
-      </c>
-      <c r="AD25" s="27" t="s">
-        <v>36</v>
       </c>
       <c r="AE25" s="17" t="s">
         <v>36</v>
@@ -3248,7 +3242,7 @@
       <c r="M26" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N26" s="24" t="s">
+      <c r="N26" s="26" t="s">
         <v>50</v>
       </c>
       <c r="O26" s="17" t="s">
@@ -3266,38 +3260,38 @@
       <c r="S26" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="T26" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="U26" s="27" t="s">
+      <c r="T26" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="U26" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="V26" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="V26" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="W26" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="X26" s="27" t="s">
+      <c r="W26" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="X26" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Y26" s="27" t="s">
+      <c r="Z26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Z26" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA26" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB26" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC26" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD26" s="28" t="s">
-        <v>10</v>
+      <c r="AA26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD26" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="AE26" s="17" t="s">
         <v>10</v>
@@ -3361,38 +3355,38 @@
       <c r="S27" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="T27" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U27" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="V27" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="W27" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X27" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y27" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z27" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA27" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB27" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC27" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD27" s="28" t="s">
-        <v>10</v>
+      <c r="T27" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="U27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="V27" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="W27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="X27" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y27" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z27" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA27" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD27" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="AE27" s="17" t="s">
         <v>10</v>
@@ -3456,38 +3450,38 @@
       <c r="S28" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="T28" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="U28" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="V28" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="W28" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X28" s="27" t="s">
+      <c r="T28" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="U28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="V28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="W28" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="X28" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y28" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="Y28" s="27" t="s">
+      <c r="Z28" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="Z28" s="27" t="s">
+      <c r="AA28" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="AA28" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB28" s="27" t="s">
+      <c r="AB28" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC28" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="AC28" s="27" t="s">
+      <c r="AD28" s="36" t="s">
         <v>17</v>
-      </c>
-      <c r="AD28" s="27" t="s">
-        <v>36</v>
       </c>
       <c r="AE28" s="17" t="s">
         <v>36</v>
@@ -3551,38 +3545,38 @@
       <c r="S29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T29" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="U29" s="28" t="s">
+      <c r="T29" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="U29" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="V29" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="V29" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="W29" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="X29" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y29" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z29" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA29" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB29" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC29" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD29" s="28" t="s">
-        <v>10</v>
+      <c r="W29" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="X29" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y29" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z29" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA29" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB29" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC29" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD29" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="AE29" s="17" t="s">
         <v>10</v>
@@ -3646,46 +3640,46 @@
       <c r="S30" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="T30" s="27" t="s">
+      <c r="T30" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="U30" s="27" t="s">
+      <c r="U30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="V30" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="W30" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X30" s="27" t="s">
+      <c r="V30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Y30" s="27" t="s">
+      <c r="W30" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="X30" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Z30" s="27" t="s">
+      <c r="Z30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="AA30" s="27" t="s">
+      <c r="AA30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="AB30" s="27" t="s">
+      <c r="AB30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="AC30" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD30" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE30" s="17" t="s">
-        <v>19</v>
+      <c r="AC30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD30" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE30" s="26" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="12.75">
       <c r="A31" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
@@ -3741,38 +3735,38 @@
       <c r="S31" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="T31" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="U31" s="27" t="s">
+      <c r="T31" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="U31" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="V31" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="V31" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="W31" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X31" s="27" t="s">
+      <c r="W31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="X31" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y31" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Y31" s="27" t="s">
+      <c r="Z31" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Z31" s="27" t="s">
+      <c r="AA31" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AA31" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB31" s="27" t="s">
+      <c r="AB31" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC31" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AC31" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD31" s="27" t="s">
-        <v>35</v>
+      <c r="AD31" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="AE31" s="17" t="s">
         <v>35</v>
@@ -3780,7 +3774,7 @@
     </row>
     <row r="32" spans="1:31" ht="12.75">
       <c r="A32" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>42</v>
@@ -3831,43 +3825,43 @@
         <v>35</v>
       </c>
       <c r="R32" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S32" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T32" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U32" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="V32" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="W32" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="X32" s="27" t="s">
+      <c r="T32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="U32" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="V32" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="W32" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="X32" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y32" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="Y32" s="27" t="s">
+      <c r="Z32" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="Z32" s="27" t="s">
+      <c r="AA32" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="AA32" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB32" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC32" s="27" t="s">
+      <c r="AB32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD32" s="17" t="s">
         <v>41</v>
-      </c>
-      <c r="AD32" s="28" t="s">
-        <v>10</v>
       </c>
       <c r="AE32" s="17" t="s">
         <v>10</v>
@@ -3875,7 +3869,7 @@
     </row>
     <row r="33" spans="1:31" ht="12.75">
       <c r="A33" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>19</v>
@@ -3931,38 +3925,38 @@
       <c r="S33" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T33" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="U33" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="V33" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W33" s="27" t="s">
+      <c r="T33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="U33" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="V33" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="W33" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X33" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="X33" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y33" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z33" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA33" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB33" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC33" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD33" s="27" t="s">
-        <v>35</v>
+      <c r="Y33" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z33" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA33" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB33" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC33" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD33" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="AE33" s="17" t="s">
         <v>35</v>
@@ -3970,7 +3964,7 @@
     </row>
     <row r="34" spans="1:31" ht="12.75">
       <c r="A34" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
@@ -4026,38 +4020,38 @@
       <c r="S34" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="T34" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="U34" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="V34" s="27" t="s">
+      <c r="T34" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="U34" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="V34" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="W34" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="W34" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X34" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y34" s="27" t="s">
+      <c r="X34" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y34" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z34" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="Z34" s="27" t="s">
+      <c r="AA34" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="AA34" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB34" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC34" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD34" s="28" t="s">
-        <v>10</v>
+      <c r="AB34" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC34" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD34" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="AE34" s="17" t="s">
         <v>10</v>
@@ -4065,7 +4059,7 @@
     </row>
     <row r="35" spans="1:31" ht="12.75">
       <c r="A35" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>19</v>
@@ -4103,7 +4097,7 @@
       <c r="M35" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="N35" s="24" t="s">
+      <c r="N35" s="26" t="s">
         <v>31</v>
       </c>
       <c r="O35" s="17" t="s">
@@ -4121,38 +4115,38 @@
       <c r="S35" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="T35" s="27" t="s">
+      <c r="T35" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="U35" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="U35" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="V35" s="27" t="s">
+      <c r="V35" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="W35" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="W35" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="X35" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y35" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z35" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA35" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB35" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC35" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD35" s="28" t="s">
-        <v>10</v>
+      <c r="X35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y35" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z35" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA35" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB35" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC35" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD35" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="AE35" s="17" t="s">
         <v>10</v>
@@ -4160,7 +4154,7 @@
     </row>
     <row r="36" spans="1:31" ht="12.75">
       <c r="A36" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>19</v>
@@ -4216,38 +4210,38 @@
       <c r="S36" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="T36" s="28" t="s">
+      <c r="T36" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="U36" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="U36" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="V36" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="W36" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="X36" s="27" t="s">
+      <c r="V36" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="W36" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X36" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y36" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="Y36" s="27" t="s">
+      <c r="Z36" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="Z36" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA36" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB36" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC36" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD36" s="28" t="s">
-        <v>10</v>
+      <c r="AA36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD36" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="AE36" s="17" t="s">
         <v>10</v>

--- a/turnos.xlsx
+++ b/turnos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29518"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56DB66EA-ABCE-43A4-9643-58A7E169555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B0E5411-3049-4DED-B53B-E27C0C1E9561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="81">
   <si>
     <t>Sabado</t>
   </si>
@@ -529,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -622,6 +622,24 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1093,7 +1111,7 @@
       <c r="Y3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="Z3" s="30" t="s">
+      <c r="Z3" s="36" t="s">
         <v>14</v>
       </c>
       <c r="AA3" s="30" t="s">
@@ -1188,22 +1206,22 @@
       <c r="Y4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="19" t="s">
+      <c r="Z4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="19" t="s">
+      <c r="AA4" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="AB4" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC4" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD4" s="21" t="s">
+      <c r="AB4" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC4" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD4" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="AE4" s="20" t="s">
+      <c r="AE4" s="32" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1283,22 +1301,22 @@
       <c r="Y5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="Z5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE5" s="20" t="s">
+      <c r="Z5" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC5" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD5" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE5" s="32" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1378,22 +1396,22 @@
       <c r="Y6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="Z6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD6" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE6" s="19" t="s">
+      <c r="Z6" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA6" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB6" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD6" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="38" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1473,20 +1491,20 @@
       <c r="Y7" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="Z7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC7" s="19" t="s">
-        <v>13</v>
+      <c r="Z7" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC7" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AD7" s="28" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE7" s="20" t="s">
         <v>10</v>
@@ -1568,7 +1586,7 @@
       <c r="Y8" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="Z8" s="17" t="s">
+      <c r="Z8" s="16" t="s">
         <v>36</v>
       </c>
       <c r="AA8" s="17" t="s">
@@ -1663,7 +1681,7 @@
       <c r="Y9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="Z9" s="18" t="s">
+      <c r="Z9" s="35" t="s">
         <v>39</v>
       </c>
       <c r="AA9" s="18" t="s">
@@ -1758,7 +1776,7 @@
       <c r="Y10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Z10" s="17" t="s">
+      <c r="Z10" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AA10" s="17" t="s">
@@ -1771,7 +1789,7 @@
         <v>15</v>
       </c>
       <c r="AD10" s="17" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE10" s="17" t="s">
         <v>10</v>
@@ -1853,7 +1871,7 @@
       <c r="Y11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="Z11" s="17" t="s">
+      <c r="Z11" s="16" t="s">
         <v>45</v>
       </c>
       <c r="AA11" s="17" t="s">
@@ -1948,7 +1966,7 @@
       <c r="Y12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="Z12" s="17" t="s">
+      <c r="Z12" s="16" t="s">
         <v>35</v>
       </c>
       <c r="AA12" s="17" t="s">
@@ -2043,7 +2061,7 @@
       <c r="Y13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Z13" s="17" t="s">
+      <c r="Z13" s="16" t="s">
         <v>16</v>
       </c>
       <c r="AA13" s="17" t="s">
@@ -2138,7 +2156,7 @@
       <c r="Y14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="Z14" s="17" t="s">
+      <c r="Z14" s="16" t="s">
         <v>16</v>
       </c>
       <c r="AA14" s="17" t="s">
@@ -2233,7 +2251,7 @@
       <c r="Y15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="Z15" s="17" t="s">
+      <c r="Z15" s="16" t="s">
         <v>29</v>
       </c>
       <c r="AA15" s="17" t="s">
@@ -2328,7 +2346,7 @@
       <c r="Y16" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="Z16" s="17" t="s">
+      <c r="Z16" s="16" t="s">
         <v>29</v>
       </c>
       <c r="AA16" s="17" t="s">
@@ -2423,7 +2441,7 @@
       <c r="Y17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="Z17" s="17" t="s">
+      <c r="Z17" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AA17" s="17" t="s">
@@ -2518,7 +2536,7 @@
       <c r="Y18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="Z18" s="17" t="s">
+      <c r="Z18" s="16" t="s">
         <v>45</v>
       </c>
       <c r="AA18" s="17" t="s">
@@ -2613,7 +2631,7 @@
       <c r="Y19" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Z19" s="17" t="s">
+      <c r="Z19" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AA19" s="17" t="s">
@@ -2708,7 +2726,7 @@
       <c r="Y20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="Z20" s="18" t="s">
+      <c r="Z20" s="35" t="s">
         <v>36</v>
       </c>
       <c r="AA20" s="18" t="s">
@@ -2803,7 +2821,7 @@
       <c r="Y21" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Z21" s="17" t="s">
+      <c r="Z21" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AA21" s="17" t="s">
@@ -2898,7 +2916,7 @@
       <c r="Y22" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="Z22" s="17" t="s">
+      <c r="Z22" s="34" t="s">
         <v>11</v>
       </c>
       <c r="AA22" s="17" t="s">
@@ -2993,7 +3011,7 @@
       <c r="Y23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="Z23" s="17" t="s">
+      <c r="Z23" s="16" t="s">
         <v>17</v>
       </c>
       <c r="AA23" s="17" t="s">
@@ -3088,7 +3106,7 @@
       <c r="Y24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="Z24" s="17" t="s">
+      <c r="Z24" s="16" t="s">
         <v>36</v>
       </c>
       <c r="AA24" s="17" t="s">
@@ -3098,10 +3116,10 @@
         <v>44</v>
       </c>
       <c r="AC24" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD24" s="17" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="AD24" s="26" t="s">
+        <v>15</v>
       </c>
       <c r="AE24" s="17" t="s">
         <v>10</v>
@@ -3183,7 +3201,7 @@
       <c r="Y25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="Z25" s="17" t="s">
+      <c r="Z25" s="16" t="s">
         <v>42</v>
       </c>
       <c r="AA25" s="17" t="s">
@@ -3195,8 +3213,8 @@
       <c r="AC25" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="AD25" s="17" t="s">
-        <v>42</v>
+      <c r="AD25" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="AE25" s="17" t="s">
         <v>36</v>
@@ -3278,7 +3296,7 @@
       <c r="Y26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Z26" s="17" t="s">
+      <c r="Z26" s="16" t="s">
         <v>22</v>
       </c>
       <c r="AA26" s="17" t="s">
@@ -3291,7 +3309,7 @@
         <v>11</v>
       </c>
       <c r="AD26" s="17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AE26" s="17" t="s">
         <v>10</v>
@@ -3373,7 +3391,7 @@
       <c r="Y27" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="Z27" s="17" t="s">
+      <c r="Z27" s="16" t="s">
         <v>20</v>
       </c>
       <c r="AA27" s="17" t="s">
@@ -3382,9 +3400,7 @@
       <c r="AB27" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AC27" s="17" t="s">
-        <v>19</v>
-      </c>
+      <c r="AC27" s="42"/>
       <c r="AD27" s="17" t="s">
         <v>16</v>
       </c>
@@ -3468,7 +3484,7 @@
       <c r="Y28" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="Z28" s="17" t="s">
+      <c r="Z28" s="16" t="s">
         <v>44</v>
       </c>
       <c r="AA28" s="17" t="s">
@@ -3480,7 +3496,7 @@
       <c r="AC28" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="AD28" s="36" t="s">
+      <c r="AD28" s="42" t="s">
         <v>17</v>
       </c>
       <c r="AE28" s="17" t="s">
@@ -3563,7 +3579,7 @@
       <c r="Y29" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="Z29" s="17" t="s">
+      <c r="Z29" s="16" t="s">
         <v>20</v>
       </c>
       <c r="AA29" s="17" t="s">
@@ -3658,7 +3674,7 @@
       <c r="Y30" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="Z30" s="17" t="s">
+      <c r="Z30" s="16" t="s">
         <v>13</v>
       </c>
       <c r="AA30" s="17" t="s">
@@ -3753,7 +3769,7 @@
       <c r="Y31" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Z31" s="17" t="s">
+      <c r="Z31" s="16" t="s">
         <v>22</v>
       </c>
       <c r="AA31" s="17" t="s">
@@ -3848,7 +3864,7 @@
       <c r="Y32" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="Z32" s="17" t="s">
+      <c r="Z32" s="16" t="s">
         <v>44</v>
       </c>
       <c r="AA32" s="17" t="s">
@@ -3860,8 +3876,8 @@
       <c r="AC32" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="AD32" s="17" t="s">
-        <v>41</v>
+      <c r="AD32" s="26" t="s">
+        <v>15</v>
       </c>
       <c r="AE32" s="17" t="s">
         <v>10</v>
@@ -3943,7 +3959,7 @@
       <c r="Y33" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Z33" s="17" t="s">
+      <c r="Z33" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AA33" s="17" t="s">
@@ -4038,14 +4054,14 @@
       <c r="Y34" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="Z34" s="17" t="s">
+      <c r="Z34" s="16" t="s">
         <v>41</v>
       </c>
       <c r="AA34" s="17" t="s">
         <v>41</v>
       </c>
       <c r="AB34" s="17" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AC34" s="17" t="s">
         <v>36</v>
@@ -4133,7 +4149,7 @@
       <c r="Y35" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Z35" s="17" t="s">
+      <c r="Z35" s="16" t="s">
         <v>16</v>
       </c>
       <c r="AA35" s="17" t="s">
@@ -4228,7 +4244,7 @@
       <c r="Y36" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="Z36" s="17" t="s">
+      <c r="Z36" s="16" t="s">
         <v>21</v>
       </c>
       <c r="AA36" s="17" t="s">
@@ -4240,8 +4256,8 @@
       <c r="AC36" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="AD36" s="17" t="s">
-        <v>15</v>
+      <c r="AD36" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="AE36" s="17" t="s">
         <v>10</v>
